--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -23465,7 +23465,7 @@
         </is>
       </c>
       <c r="B2314" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2315">
@@ -23475,7 +23475,7 @@
         </is>
       </c>
       <c r="B2315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2316">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="B2318" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2319">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1534">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="B1543" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1544">
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="B1577" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1578">
@@ -17085,7 +17085,7 @@
         </is>
       </c>
       <c r="B1673" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1674">
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="B1771" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1772">
@@ -18115,7 +18115,7 @@
         </is>
       </c>
       <c r="B1776" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1777">
@@ -18135,7 +18135,7 @@
         </is>
       </c>
       <c r="B1778" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1779">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="B1803" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1804">
@@ -18675,7 +18675,7 @@
         </is>
       </c>
       <c r="B1832" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1833">
@@ -18922,7 +18922,7 @@
         </is>
       </c>
       <c r="B1857" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1858">
@@ -18932,7 +18932,7 @@
         </is>
       </c>
       <c r="B1858" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1859">
@@ -19232,7 +19232,7 @@
         </is>
       </c>
       <c r="B1888" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1889">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -13000,7 +13000,7 @@
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1261">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -18135,7 +18135,7 @@
         </is>
       </c>
       <c r="B1778" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1779">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="B1779" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1780">
@@ -18155,7 +18155,7 @@
         </is>
       </c>
       <c r="B1780" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1781">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1034">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1368">
@@ -14068,7 +14068,7 @@
         </is>
       </c>
       <c r="B1368" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1369">
@@ -14268,7 +14268,7 @@
         </is>
       </c>
       <c r="B1388" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1389">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1395">
@@ -14338,7 +14338,7 @@
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1396">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1400">
@@ -14388,7 +14388,7 @@
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1401">
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="B1402" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1403">
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1417" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1418">
@@ -19032,7 +19032,7 @@
         </is>
       </c>
       <c r="B1868" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1869">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1184">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1289">
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1292">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1446">
@@ -14848,7 +14848,7 @@
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1447">
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="B1782" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1783">
@@ -18195,7 +18195,7 @@
         </is>
       </c>
       <c r="B1784" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1785">
@@ -18982,7 +18982,7 @@
         </is>
       </c>
       <c r="B1863" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1864">
@@ -19222,7 +19222,7 @@
         </is>
       </c>
       <c r="B1887" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1888">
@@ -19232,7 +19232,7 @@
         </is>
       </c>
       <c r="B1888" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1889">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -19292,7 +19292,7 @@
         </is>
       </c>
       <c r="B1894" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1895">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1251">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="B1779" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1780">
@@ -18155,7 +18155,7 @@
         </is>
       </c>
       <c r="B1780" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1781">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -443,6 +443,9 @@
           <t>KAKITAR</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,6 +663,9 @@
           <t>1000B</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -807,6 +813,9 @@
           <t>BH651DIR</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1195,7 +1204,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -1235,7 +1244,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2074,6 +2083,9 @@
           <t>DRX16514SS</t>
         </is>
       </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2221,6 +2233,9 @@
           <t>PDEXT16IN</t>
         </is>
       </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2228,6 +2243,9 @@
           <t>PDEXT16SB</t>
         </is>
       </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2255,6 +2273,9 @@
           <t>PDX722LMBF</t>
         </is>
       </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3243,7 +3264,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -3313,7 +3334,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292">
@@ -3323,7 +3344,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -3343,7 +3364,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295">
@@ -3403,7 +3424,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -3483,7 +3504,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
@@ -3493,7 +3514,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -3593,7 +3614,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -3733,7 +3754,7 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -3893,7 +3914,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -4183,7 +4204,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -4463,7 +4484,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -4902,6 +4923,9 @@
           <t>AZ2204NWGR</t>
         </is>
       </c>
+      <c r="B450" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -5000,7 +5024,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -5430,7 +5454,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="504">
@@ -5600,7 +5624,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="521">
@@ -5630,7 +5654,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -5860,7 +5884,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -5980,7 +6004,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -6070,7 +6094,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -6100,7 +6124,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="571">
@@ -6160,7 +6184,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -6240,7 +6264,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="585">
@@ -6280,7 +6304,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="589">
@@ -6390,7 +6414,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -6420,7 +6444,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -6470,7 +6494,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="608">
@@ -6560,7 +6584,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -6650,7 +6674,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626">
@@ -6770,7 +6794,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -7040,7 +7064,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="665">
@@ -7400,7 +7424,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="701">
@@ -7500,7 +7524,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="711">
@@ -7660,7 +7684,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="727">
@@ -7730,7 +7754,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
@@ -7760,7 +7784,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="737">
@@ -7780,7 +7804,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739">
@@ -7830,7 +7854,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="744">
@@ -7990,7 +8014,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="760">
@@ -8060,7 +8084,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="767">
@@ -8479,6 +8503,9 @@
           <t>TCY10ETBS</t>
         </is>
       </c>
+      <c r="B808" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -8507,7 +8534,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
@@ -8557,7 +8584,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="817">
@@ -8777,7 +8804,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="839">
@@ -8916,6 +8943,9 @@
           <t>BP5</t>
         </is>
       </c>
+      <c r="B852" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -8944,7 +8974,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="856">
@@ -9144,7 +9174,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
@@ -9394,7 +9424,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="901">
@@ -9424,7 +9454,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="904">
@@ -9444,7 +9474,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="906">
@@ -9454,7 +9484,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="907">
@@ -9464,7 +9494,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
@@ -9474,7 +9504,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="909">
@@ -9554,7 +9584,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="917">
@@ -9584,7 +9614,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="920">
@@ -9614,7 +9644,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="923">
@@ -9644,7 +9674,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="926">
@@ -9664,7 +9694,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="928">
@@ -9694,7 +9724,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="931">
@@ -9994,7 +10024,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="961">
@@ -10084,7 +10114,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="970">
@@ -10594,7 +10624,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1021">
@@ -10604,7 +10634,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1022">
@@ -10614,7 +10644,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1023">
@@ -10724,7 +10754,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1034">
@@ -10794,7 +10824,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1041">
@@ -10844,7 +10874,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1046">
@@ -10974,7 +11004,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1059">
@@ -11074,7 +11104,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1069">
@@ -11544,7 +11574,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1116">
@@ -11764,7 +11794,7 @@
         </is>
       </c>
       <c r="B1137" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1138">
@@ -11844,7 +11874,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1146">
@@ -11884,7 +11914,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1150">
@@ -11894,7 +11924,7 @@
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1151">
@@ -12924,7 +12954,7 @@
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1254">
@@ -12994,7 +13024,7 @@
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1261">
@@ -13274,7 +13304,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1289">
@@ -13304,7 +13334,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1292">
@@ -13364,7 +13394,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1298">
@@ -13383,6 +13413,9 @@
           <t>LC266F1DIR</t>
         </is>
       </c>
+      <c r="B1299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
@@ -13391,7 +13424,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1301">
@@ -13411,7 +13444,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1303">
@@ -13531,7 +13564,7 @@
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1315">
@@ -13620,6 +13653,9 @@
           <t>PDBO</t>
         </is>
       </c>
+      <c r="B1323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
@@ -13627,6 +13663,9 @@
           <t>PIEGRONS</t>
         </is>
       </c>
+      <c r="B1324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
@@ -13664,6 +13703,9 @@
           <t>TOM13 AA</t>
         </is>
       </c>
+      <c r="B1328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
@@ -13682,7 +13724,7 @@
         </is>
       </c>
       <c r="B1330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1331">
@@ -14622,7 +14664,7 @@
         </is>
       </c>
       <c r="B1424" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1425">
@@ -14642,7 +14684,7 @@
         </is>
       </c>
       <c r="B1426" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1427">
@@ -14832,7 +14874,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1446">
@@ -14872,7 +14914,7 @@
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1450">
@@ -14882,7 +14924,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1451">
@@ -14892,7 +14934,7 @@
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1452">
@@ -14948,17 +14990,17 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>FR1XB-BK</t>
+          <t>APC33</t>
         </is>
       </c>
       <c r="B1457" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>FR3X BK</t>
+          <t>BCB60</t>
         </is>
       </c>
       <c r="B1458" t="n">
@@ -14968,37 +15010,37 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>FR4X RD</t>
+          <t>BICB10ABK</t>
         </is>
       </c>
       <c r="B1459" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>FR7X BK</t>
+          <t>BICB10ABU</t>
         </is>
       </c>
       <c r="B1460" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>FR8X BK</t>
+          <t>BICB10AGN</t>
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>APC33</t>
+          <t>BICB10AOR</t>
         </is>
       </c>
       <c r="B1462" t="n">
@@ -15008,17 +15050,17 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>BCB60</t>
+          <t>BICB10ARD</t>
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>BICB10ABK</t>
+          <t>BICB10AYL</t>
         </is>
       </c>
       <c r="B1464" t="n">
@@ -15028,74 +15070,77 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>BICB10ABU</t>
+          <t>CDIBR1</t>
         </is>
       </c>
       <c r="B1465" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>BICB10AGN</t>
+          <t>CYM10</t>
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>BICB10AOR</t>
+          <t>DB30</t>
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>BICB10ARD</t>
+          <t>DB60</t>
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>BICB10AYL</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="B1469" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>CDIBR1</t>
-        </is>
+          <t>FPS9</t>
+        </is>
+      </c>
+      <c r="B1470" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>CYM10</t>
+          <t>GKC10</t>
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>DB30</t>
+          <t>HDP25K100</t>
         </is>
       </c>
       <c r="B1472" t="n">
@@ -15105,14 +15150,17 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>DB60</t>
-        </is>
+          <t>HDP35-40G</t>
+        </is>
+      </c>
+      <c r="B1473" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>KDFE50BK</t>
         </is>
       </c>
       <c r="B1474" t="n">
@@ -15122,17 +15170,17 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>FPS9</t>
+          <t>KP24</t>
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>GKC10</t>
+          <t>KSC70BK</t>
         </is>
       </c>
       <c r="B1476" t="n">
@@ -15142,27 +15190,27 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>HDP25K100</t>
+          <t>KSC70WH</t>
         </is>
       </c>
       <c r="B1477" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>HDP35-40G</t>
+          <t>KSC72BK</t>
         </is>
       </c>
       <c r="B1478" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>KDFE50BK</t>
+          <t>KSC80CR</t>
         </is>
       </c>
       <c r="B1479" t="n">
@@ -15172,114 +15220,117 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>KP24</t>
+          <t>KSC82PE</t>
         </is>
       </c>
       <c r="B1480" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>KSC70BK</t>
+          <t>KSCFP10BK</t>
         </is>
       </c>
       <c r="B1481" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>KSC70WH</t>
+          <t>KSFE50BK</t>
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>KSC72BK</t>
+          <t>KSH704/2DR</t>
         </is>
       </c>
       <c r="B1483" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>KSC80CR</t>
+          <t>KSH704/2PE</t>
         </is>
       </c>
       <c r="B1484" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>KSC82PE</t>
-        </is>
+          <t>KSH704/2WH</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>KSCFP10BK</t>
+          <t>KSH704LA</t>
         </is>
       </c>
       <c r="B1486" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>KSFE50BK</t>
+          <t>KSL5PE</t>
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>KSH704/2DR</t>
+          <t>KSL6PE</t>
         </is>
       </c>
       <c r="B1488" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>KSH704/2PE</t>
+          <t>KSL705PE</t>
         </is>
       </c>
       <c r="B1489" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>KSH704/2WH</t>
+          <t>KSL706PE</t>
         </is>
       </c>
       <c r="B1490" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>KSH704LA</t>
+          <t>MCB1</t>
         </is>
       </c>
       <c r="B1491" t="n">
@@ -15289,118 +15340,127 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>KSL5PE</t>
+          <t>PSA230S</t>
         </is>
       </c>
       <c r="B1492" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>KSL6PE</t>
-        </is>
+          <t>RICB10</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>KSL705PE</t>
-        </is>
+          <t>RICB10A</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>KSL706PE</t>
-        </is>
+          <t>RICB20</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>MCB1</t>
+          <t>RICB20A</t>
         </is>
       </c>
       <c r="B1496" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>PSA230S</t>
+          <t>RMCB15</t>
         </is>
       </c>
       <c r="B1497" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>RICB10</t>
+          <t>RMIDIB15</t>
         </is>
       </c>
       <c r="B1498" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>RICB10A</t>
+          <t>RUBIX22</t>
         </is>
       </c>
       <c r="B1499" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>RICB20</t>
+          <t>RUBIX24</t>
         </is>
       </c>
       <c r="B1500" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>RICB20A</t>
+          <t>SCW100S</t>
         </is>
       </c>
       <c r="B1501" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>RMCB15</t>
+          <t>TU01</t>
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>RMIDIB15</t>
+          <t>TU02</t>
         </is>
       </c>
       <c r="B1503" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>RUBIX22</t>
+          <t>TU05</t>
         </is>
       </c>
       <c r="B1504" t="n">
@@ -15410,47 +15470,47 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>RUBIX24</t>
+          <t>TU12BW</t>
         </is>
       </c>
       <c r="B1505" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>SCW100S</t>
+          <t>TU12EX</t>
         </is>
       </c>
       <c r="B1506" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>TU01</t>
+          <t>TU12H</t>
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>TU02</t>
+          <t>UA11MKII</t>
         </is>
       </c>
       <c r="B1508" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>TU05</t>
+          <t>UA1EX</t>
         </is>
       </c>
       <c r="B1509" t="n">
@@ -15460,7 +15520,7 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>TU12BW</t>
+          <t>UA55</t>
         </is>
       </c>
       <c r="B1510" t="n">
@@ -15470,7 +15530,7 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>TU12EX</t>
+          <t>UM ONE MK2</t>
         </is>
       </c>
       <c r="B1511" t="n">
@@ -15480,7 +15540,7 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>TU12H</t>
+          <t>VS24MBA</t>
         </is>
       </c>
       <c r="B1512" t="n">
@@ -15490,7 +15550,7 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>UA11MKII</t>
+          <t>VS880S1</t>
         </is>
       </c>
       <c r="B1513" t="n">
@@ -15500,7 +15560,7 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>UA1EX</t>
+          <t>FR1XB-BK</t>
         </is>
       </c>
       <c r="B1514" t="n">
@@ -15510,7 +15570,7 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>UA55</t>
+          <t>FR3X BK</t>
         </is>
       </c>
       <c r="B1515" t="n">
@@ -15520,17 +15580,17 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>UM ONE MK2</t>
+          <t>FR4X RD</t>
         </is>
       </c>
       <c r="B1516" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>VS24MBA</t>
+          <t>FR7X BK</t>
         </is>
       </c>
       <c r="B1517" t="n">
@@ -15540,7 +15600,7 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>VS880S1</t>
+          <t>FR8X BK</t>
         </is>
       </c>
       <c r="B1518" t="n">
@@ -15943,6 +16003,9 @@
           <t>MDH10U</t>
         </is>
       </c>
+      <c r="B1558" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
@@ -15951,7 +16014,7 @@
         </is>
       </c>
       <c r="B1559" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1560">
@@ -15960,6 +16023,9 @@
           <t>MDS STG2</t>
         </is>
       </c>
+      <c r="B1560" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
@@ -15977,6 +16043,9 @@
           <t>MDS4C</t>
         </is>
       </c>
+      <c r="B1562" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
@@ -15984,6 +16053,9 @@
           <t>MDS4V</t>
         </is>
       </c>
+      <c r="B1563" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
@@ -15991,6 +16063,9 @@
           <t>MDS50K</t>
         </is>
       </c>
+      <c r="B1564" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
@@ -16018,6 +16093,9 @@
           <t>MDS9V</t>
         </is>
       </c>
+      <c r="B1567" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
@@ -16026,7 +16104,7 @@
         </is>
       </c>
       <c r="B1568" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1569">
@@ -16046,7 +16124,7 @@
         </is>
       </c>
       <c r="B1570" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1571">
@@ -16055,6 +16133,9 @@
           <t>MH10</t>
         </is>
       </c>
+      <c r="B1571" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
@@ -16243,7 +16324,7 @@
         </is>
       </c>
       <c r="B1590" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1591">
@@ -17603,7 +17684,7 @@
         </is>
       </c>
       <c r="B1726" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1727">
@@ -17633,7 +17714,7 @@
         </is>
       </c>
       <c r="B1729" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1730">
@@ -18053,7 +18134,7 @@
         </is>
       </c>
       <c r="B1771" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1772">
@@ -18443,7 +18524,7 @@
         </is>
       </c>
       <c r="B1810" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1811">
@@ -18473,7 +18554,7 @@
         </is>
       </c>
       <c r="B1813" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1814">
@@ -18753,7 +18834,7 @@
         </is>
       </c>
       <c r="B1841" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1842">
@@ -18832,6 +18913,9 @@
           <t>RS70S</t>
         </is>
       </c>
+      <c r="B1849" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1850">
       <c r="A1850" t="inlineStr">
@@ -19170,43 +19254,43 @@
         </is>
       </c>
       <c r="B1883" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1884">
       <c r="A1884" t="inlineStr">
         <is>
-          <t>GA112</t>
+          <t>EF303</t>
         </is>
       </c>
       <c r="B1884" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1885">
       <c r="A1885" t="inlineStr">
         <is>
-          <t>GO MIXER</t>
+          <t>GA112</t>
         </is>
       </c>
       <c r="B1885" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1886">
       <c r="A1886" t="inlineStr">
         <is>
-          <t>GO MIXERPX</t>
+          <t>GO MIXER</t>
         </is>
       </c>
       <c r="B1886" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1887">
       <c r="A1887" t="inlineStr">
         <is>
-          <t>GOLIVECAST</t>
+          <t>GO MIXERPX</t>
         </is>
       </c>
       <c r="B1887" t="n">
@@ -19216,67 +19300,67 @@
     <row r="1888">
       <c r="A1888" t="inlineStr">
         <is>
-          <t>JC120B</t>
+          <t>GOLIVECAST</t>
         </is>
       </c>
       <c r="B1888" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1889">
       <c r="A1889" t="inlineStr">
         <is>
-          <t>JC120G</t>
+          <t>JC120B</t>
         </is>
       </c>
       <c r="B1889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1890">
       <c r="A1890" t="inlineStr">
         <is>
-          <t>JC22</t>
+          <t>JC120G</t>
         </is>
       </c>
       <c r="B1890" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1891">
       <c r="A1891" t="inlineStr">
         <is>
-          <t>JC40</t>
+          <t>JC22</t>
         </is>
       </c>
       <c r="B1891" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1892">
       <c r="A1892" t="inlineStr">
         <is>
-          <t>K25M</t>
+          <t>JC40</t>
         </is>
       </c>
       <c r="B1892" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1893">
       <c r="A1893" t="inlineStr">
         <is>
-          <t>KATANA GO</t>
+          <t>K25M</t>
         </is>
       </c>
       <c r="B1893" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1894">
       <c r="A1894" t="inlineStr">
         <is>
-          <t>KC550</t>
+          <t>KATANA GO</t>
         </is>
       </c>
       <c r="B1894" t="n">
@@ -19286,7 +19370,7 @@
     <row r="1895">
       <c r="A1895" t="inlineStr">
         <is>
-          <t>KTN HEAD</t>
+          <t>KC550</t>
         </is>
       </c>
       <c r="B1895" t="n">
@@ -19296,27 +19380,27 @@
     <row r="1896">
       <c r="A1896" t="inlineStr">
         <is>
-          <t>KTN MINI</t>
+          <t>KTN HEAD</t>
         </is>
       </c>
       <c r="B1896" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1897">
       <c r="A1897" t="inlineStr">
         <is>
-          <t>KTN100</t>
+          <t>KTN MINI</t>
         </is>
       </c>
       <c r="B1897" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1898">
       <c r="A1898" t="inlineStr">
         <is>
-          <t>KTN100 3</t>
+          <t>KTN100</t>
         </is>
       </c>
       <c r="B1898" t="n">
@@ -19326,7 +19410,7 @@
     <row r="1899">
       <c r="A1899" t="inlineStr">
         <is>
-          <t>KTN100MKII</t>
+          <t>KTN100 3</t>
         </is>
       </c>
       <c r="B1899" t="n">
@@ -19336,7 +19420,7 @@
     <row r="1900">
       <c r="A1900" t="inlineStr">
         <is>
-          <t>KTN212MKII</t>
+          <t>KTN100MKII</t>
         </is>
       </c>
       <c r="B1900" t="n">
@@ -19346,17 +19430,17 @@
     <row r="1901">
       <c r="A1901" t="inlineStr">
         <is>
-          <t>KTN50 3</t>
+          <t>KTN212MKII</t>
         </is>
       </c>
       <c r="B1901" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1902">
       <c r="A1902" t="inlineStr">
         <is>
-          <t>KTN50 3EX</t>
+          <t>KTN50 3</t>
         </is>
       </c>
       <c r="B1902" t="n">
@@ -19366,27 +19450,27 @@
     <row r="1903">
       <c r="A1903" t="inlineStr">
         <is>
-          <t>KTN50 MKII</t>
+          <t>KTN50 3EX</t>
         </is>
       </c>
       <c r="B1903" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1904">
       <c r="A1904" t="inlineStr">
         <is>
-          <t>KTNGO2</t>
+          <t>KTN50 MKII</t>
         </is>
       </c>
       <c r="B1904" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1905">
       <c r="A1905" t="inlineStr">
         <is>
-          <t>KTNMINI X</t>
+          <t>KTNGO2</t>
         </is>
       </c>
       <c r="B1905" t="n">
@@ -19396,27 +19480,27 @@
     <row r="1906">
       <c r="A1906" t="inlineStr">
         <is>
-          <t>M48</t>
+          <t>KTNMINI X</t>
         </is>
       </c>
       <c r="B1906" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1907">
       <c r="A1907" t="inlineStr">
         <is>
-          <t>M480</t>
+          <t>M48</t>
         </is>
       </c>
       <c r="B1907" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1908">
       <c r="A1908" t="inlineStr">
         <is>
-          <t>M5000</t>
+          <t>M480</t>
         </is>
       </c>
       <c r="B1908" t="n">
@@ -19426,17 +19510,17 @@
     <row r="1909">
       <c r="A1909" t="inlineStr">
         <is>
-          <t>R07BK</t>
+          <t>M5000</t>
         </is>
       </c>
       <c r="B1909" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1910">
       <c r="A1910" t="inlineStr">
         <is>
-          <t>R44E</t>
+          <t>R07BK</t>
         </is>
       </c>
       <c r="B1910" t="n">
@@ -19446,7 +19530,7 @@
     <row r="1911">
       <c r="A1911" t="inlineStr">
         <is>
-          <t>R88</t>
+          <t>R44E</t>
         </is>
       </c>
       <c r="B1911" t="n">
@@ -19456,24 +19540,27 @@
     <row r="1912">
       <c r="A1912" t="inlineStr">
         <is>
-          <t>RPW7</t>
+          <t>R88</t>
         </is>
       </c>
       <c r="B1912" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1913">
       <c r="A1913" t="inlineStr">
         <is>
-          <t>S0808</t>
-        </is>
+          <t>RPW7</t>
+        </is>
+      </c>
+      <c r="B1913" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1914">
       <c r="A1914" t="inlineStr">
         <is>
-          <t>S0816</t>
+          <t>S0808</t>
         </is>
       </c>
       <c r="B1914" t="n">
@@ -19483,37 +19570,37 @@
     <row r="1915">
       <c r="A1915" t="inlineStr">
         <is>
-          <t>S1608</t>
+          <t>S0816</t>
         </is>
       </c>
       <c r="B1915" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1916">
       <c r="A1916" t="inlineStr">
         <is>
-          <t>S2416</t>
+          <t>S1608</t>
         </is>
       </c>
       <c r="B1916" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1917">
       <c r="A1917" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>S2416</t>
         </is>
       </c>
       <c r="B1917" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1918">
       <c r="A1918" t="inlineStr">
         <is>
-          <t>TR8S</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="B1918" t="n">
@@ -19523,17 +19610,17 @@
     <row r="1919">
       <c r="A1919" t="inlineStr">
         <is>
-          <t>V02HD</t>
+          <t>TR8S</t>
         </is>
       </c>
       <c r="B1919" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1920">
       <c r="A1920" t="inlineStr">
         <is>
-          <t>V02HDMK2</t>
+          <t>V02HD</t>
         </is>
       </c>
       <c r="B1920" t="n">
@@ -19543,67 +19630,67 @@
     <row r="1921">
       <c r="A1921" t="inlineStr">
         <is>
-          <t>V1HD</t>
+          <t>V02HDMK2</t>
         </is>
       </c>
       <c r="B1921" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1922">
       <c r="A1922" t="inlineStr">
         <is>
-          <t>V1HD PLUS</t>
+          <t>V1HD</t>
         </is>
       </c>
       <c r="B1922" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1923">
       <c r="A1923" t="inlineStr">
         <is>
-          <t>V1SDI</t>
+          <t>V1HD PLUS</t>
         </is>
       </c>
       <c r="B1923" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1924">
       <c r="A1924" t="inlineStr">
         <is>
-          <t>V4EX</t>
+          <t>V1SDI</t>
         </is>
       </c>
       <c r="B1924" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1925">
       <c r="A1925" t="inlineStr">
         <is>
-          <t>V800HD</t>
+          <t>V4EX</t>
         </is>
       </c>
       <c r="B1925" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1926">
       <c r="A1926" t="inlineStr">
         <is>
-          <t>VC1DL</t>
+          <t>V800HD</t>
         </is>
       </c>
       <c r="B1926" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1927">
       <c r="A1927" t="inlineStr">
         <is>
-          <t>VC1HS</t>
+          <t>VC1DL</t>
         </is>
       </c>
       <c r="B1927" t="n">
@@ -19613,7 +19700,7 @@
     <row r="1928">
       <c r="A1928" t="inlineStr">
         <is>
-          <t>VC1SH</t>
+          <t>VC1HS</t>
         </is>
       </c>
       <c r="B1928" t="n">
@@ -19623,7 +19710,7 @@
     <row r="1929">
       <c r="A1929" t="inlineStr">
         <is>
-          <t>VR 1HD</t>
+          <t>VC1SH</t>
         </is>
       </c>
       <c r="B1929" t="n">
@@ -19633,7 +19720,7 @@
     <row r="1930">
       <c r="A1930" t="inlineStr">
         <is>
-          <t>VR 4HD</t>
+          <t>VR 1HD</t>
         </is>
       </c>
       <c r="B1930" t="n">
@@ -19643,7 +19730,7 @@
     <row r="1931">
       <c r="A1931" t="inlineStr">
         <is>
-          <t>VRC-01</t>
+          <t>VR 4HD</t>
         </is>
       </c>
       <c r="B1931" t="n">
@@ -19653,24 +19740,27 @@
     <row r="1932">
       <c r="A1932" t="inlineStr">
         <is>
-          <t>VT4</t>
+          <t>VRC-01</t>
         </is>
       </c>
       <c r="B1932" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1933">
       <c r="A1933" t="inlineStr">
         <is>
-          <t>XI-DANTE</t>
-        </is>
+          <t>VT4</t>
+        </is>
+      </c>
+      <c r="B1933" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="1934">
       <c r="A1934" t="inlineStr">
         <is>
-          <t>14WBFSK</t>
+          <t>XI-DANTE</t>
         </is>
       </c>
       <c r="B1934" t="n">
@@ -19680,7 +19770,7 @@
     <row r="1935">
       <c r="A1935" t="inlineStr">
         <is>
-          <t>1691DZ</t>
+          <t>14WBFSK</t>
         </is>
       </c>
       <c r="B1935" t="n">
@@ -19690,7 +19780,7 @@
     <row r="1936">
       <c r="A1936" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1691DZ</t>
         </is>
       </c>
       <c r="B1936" t="n">
@@ -19700,14 +19790,17 @@
     <row r="1937">
       <c r="A1937" t="inlineStr">
         <is>
-          <t>1702DZ</t>
-        </is>
+          <t>1698</t>
+        </is>
+      </c>
+      <c r="B1937" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1938">
       <c r="A1938" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1702DZ</t>
         </is>
       </c>
       <c r="B1938" t="n">
@@ -19717,37 +19810,37 @@
     <row r="1939">
       <c r="A1939" t="inlineStr">
         <is>
-          <t>1714DZ</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="B1939" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1940">
       <c r="A1940" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1714DZ</t>
         </is>
       </c>
       <c r="B1940" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1941">
       <c r="A1941" t="inlineStr">
         <is>
-          <t>1715DZ</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="B1941" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1942">
       <c r="A1942" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1715DZ</t>
         </is>
       </c>
       <c r="B1942" t="n">
@@ -19757,7 +19850,7 @@
     <row r="1943">
       <c r="A1943" t="inlineStr">
         <is>
-          <t>1719DZ</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="B1943" t="n">
@@ -19767,47 +19860,47 @@
     <row r="1944">
       <c r="A1944" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1719DZ</t>
         </is>
       </c>
       <c r="B1944" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1945">
       <c r="A1945" t="inlineStr">
         <is>
-          <t>1720DZ</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B1945" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1946">
       <c r="A1946" t="inlineStr">
         <is>
-          <t>1721DZ</t>
+          <t>1720DZ</t>
         </is>
       </c>
       <c r="B1946" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1947">
       <c r="A1947" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1721DZ</t>
         </is>
       </c>
       <c r="B1947" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1948">
       <c r="A1948" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="B1948" t="n">
@@ -19817,57 +19910,57 @@
     <row r="1949">
       <c r="A1949" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="B1949" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1950">
       <c r="A1950" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="B1950" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1951">
       <c r="A1951" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="B1951" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1952">
       <c r="A1952" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="B1952" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1953">
       <c r="A1953" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="B1953" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1954">
       <c r="A1954" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="B1954" t="n">
@@ -19877,7 +19970,7 @@
     <row r="1955">
       <c r="A1955" t="inlineStr">
         <is>
-          <t>2942B</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="B1955" t="n">
@@ -19887,7 +19980,7 @@
     <row r="1956">
       <c r="A1956" t="inlineStr">
         <is>
-          <t>3107TRB</t>
+          <t>2942B</t>
         </is>
       </c>
       <c r="B1956" t="n">
@@ -19897,7 +19990,7 @@
     <row r="1957">
       <c r="A1957" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>3107TRB</t>
         </is>
       </c>
       <c r="B1957" t="n">
@@ -19907,7 +20000,7 @@
     <row r="1958">
       <c r="A1958" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>31379</t>
         </is>
       </c>
       <c r="B1958" t="n">
@@ -19917,7 +20010,7 @@
     <row r="1959">
       <c r="A1959" t="inlineStr">
         <is>
-          <t>33611</t>
+          <t>33610</t>
         </is>
       </c>
       <c r="B1959" t="n">
@@ -19927,7 +20020,7 @@
     <row r="1960">
       <c r="A1960" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="B1960" t="n">
@@ -19937,7 +20030,7 @@
     <row r="1961">
       <c r="A1961" t="inlineStr">
         <is>
-          <t>336B</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="B1961" t="n">
@@ -19947,7 +20040,7 @@
     <row r="1962">
       <c r="A1962" t="inlineStr">
         <is>
-          <t>337AW</t>
+          <t>336B</t>
         </is>
       </c>
       <c r="B1962" t="n">
@@ -19957,17 +20050,17 @@
     <row r="1963">
       <c r="A1963" t="inlineStr">
         <is>
-          <t>337B</t>
+          <t>337AW</t>
         </is>
       </c>
       <c r="B1963" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1964">
       <c r="A1964" t="inlineStr">
         <is>
-          <t>337BRL</t>
+          <t>337B</t>
         </is>
       </c>
       <c r="B1964" t="n">
@@ -19977,7 +20070,7 @@
     <row r="1965">
       <c r="A1965" t="inlineStr">
         <is>
-          <t>337BRS</t>
+          <t>337BRL</t>
         </is>
       </c>
       <c r="B1965" t="n">
@@ -19987,7 +20080,7 @@
     <row r="1966">
       <c r="A1966" t="inlineStr">
         <is>
-          <t>337C</t>
+          <t>337BRS</t>
         </is>
       </c>
       <c r="B1966" t="n">
@@ -19997,17 +20090,17 @@
     <row r="1967">
       <c r="A1967" t="inlineStr">
         <is>
-          <t>337L</t>
+          <t>337C</t>
         </is>
       </c>
       <c r="B1967" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1968">
       <c r="A1968" t="inlineStr">
         <is>
-          <t>337R</t>
+          <t>337L</t>
         </is>
       </c>
       <c r="B1968" t="n">
@@ -20017,7 +20110,7 @@
     <row r="1969">
       <c r="A1969" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>337R</t>
         </is>
       </c>
       <c r="B1969" t="n">
@@ -20027,7 +20120,7 @@
     <row r="1970">
       <c r="A1970" t="inlineStr">
         <is>
-          <t>3411FG</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B1970" t="n">
@@ -20037,7 +20130,7 @@
     <row r="1971">
       <c r="A1971" t="inlineStr">
         <is>
-          <t>3411FGM</t>
+          <t>3411FG</t>
         </is>
       </c>
       <c r="B1971" t="n">
@@ -20047,7 +20140,7 @@
     <row r="1972">
       <c r="A1972" t="inlineStr">
         <is>
-          <t>3411FGW88</t>
+          <t>3411FGM</t>
         </is>
       </c>
       <c r="B1972" t="n">
@@ -20057,37 +20150,37 @@
     <row r="1973">
       <c r="A1973" t="inlineStr">
         <is>
-          <t>3411HGM</t>
+          <t>3411FGW88</t>
         </is>
       </c>
       <c r="B1973" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1974">
       <c r="A1974" t="inlineStr">
         <is>
-          <t>3414GB</t>
+          <t>3411HGM</t>
         </is>
       </c>
       <c r="B1974" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1975">
       <c r="A1975" t="inlineStr">
         <is>
-          <t>3416HA</t>
+          <t>3414GB</t>
         </is>
       </c>
       <c r="B1975" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1976">
       <c r="A1976" t="inlineStr">
         <is>
-          <t>3416HAL104</t>
+          <t>3416HA</t>
         </is>
       </c>
       <c r="B1976" t="n">
@@ -20097,14 +20190,17 @@
     <row r="1977">
       <c r="A1977" t="inlineStr">
         <is>
-          <t>35012C</t>
-        </is>
+          <t>3416HAL104</t>
+        </is>
+      </c>
+      <c r="B1977" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1978">
       <c r="A1978" t="inlineStr">
         <is>
-          <t>35015C</t>
+          <t>35012C</t>
         </is>
       </c>
       <c r="B1978" t="n">
@@ -20114,54 +20210,57 @@
     <row r="1979">
       <c r="A1979" t="inlineStr">
         <is>
-          <t>3506HAL</t>
+          <t>35015C</t>
         </is>
       </c>
       <c r="B1979" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1980">
       <c r="A1980" t="inlineStr">
         <is>
-          <t>3510HC</t>
+          <t>3506HAL</t>
         </is>
       </c>
       <c r="B1980" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>35110HC</t>
-        </is>
+          <t>3510HC</t>
+        </is>
+      </c>
+      <c r="B1981" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1982">
       <c r="A1982" t="inlineStr">
         <is>
-          <t>35110HDW</t>
+          <t>35110HC</t>
         </is>
       </c>
       <c r="B1982" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1983">
       <c r="A1983" t="inlineStr">
         <is>
-          <t>35112C</t>
+          <t>35110HDW</t>
         </is>
       </c>
       <c r="B1983" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1984">
       <c r="A1984" t="inlineStr">
         <is>
-          <t>35118</t>
+          <t>35112C</t>
         </is>
       </c>
       <c r="B1984" t="n">
@@ -20171,7 +20270,7 @@
     <row r="1985">
       <c r="A1985" t="inlineStr">
         <is>
-          <t>3511C</t>
+          <t>35118</t>
         </is>
       </c>
       <c r="B1985" t="n">
@@ -20181,7 +20280,7 @@
     <row r="1986">
       <c r="A1986" t="inlineStr">
         <is>
-          <t>3511HC</t>
+          <t>3511C</t>
         </is>
       </c>
       <c r="B1986" t="n">
@@ -20191,7 +20290,7 @@
     <row r="1987">
       <c r="A1987" t="inlineStr">
         <is>
-          <t>3513C</t>
+          <t>3511HC</t>
         </is>
       </c>
       <c r="B1987" t="n">
@@ -20201,7 +20300,7 @@
     <row r="1988">
       <c r="A1988" t="inlineStr">
         <is>
-          <t>3514B</t>
+          <t>3513C</t>
         </is>
       </c>
       <c r="B1988" t="n">
@@ -20211,37 +20310,37 @@
     <row r="1989">
       <c r="A1989" t="inlineStr">
         <is>
-          <t>3515C</t>
+          <t>3514B</t>
         </is>
       </c>
       <c r="B1989" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1990">
       <c r="A1990" t="inlineStr">
         <is>
-          <t>3517C</t>
+          <t>3515C</t>
         </is>
       </c>
       <c r="B1990" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1991">
       <c r="A1991" t="inlineStr">
         <is>
-          <t>3527LBS</t>
+          <t>3517C</t>
         </is>
       </c>
       <c r="B1991" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1992">
       <c r="A1992" t="inlineStr">
         <is>
-          <t>354L</t>
+          <t>3527LBS</t>
         </is>
       </c>
       <c r="B1992" t="n">
@@ -20251,7 +20350,7 @@
     <row r="1993">
       <c r="A1993" t="inlineStr">
         <is>
-          <t>380TB</t>
+          <t>354L</t>
         </is>
       </c>
       <c r="B1993" t="n">
@@ -20261,7 +20360,7 @@
     <row r="1994">
       <c r="A1994" t="inlineStr">
         <is>
-          <t>3817C</t>
+          <t>380TB</t>
         </is>
       </c>
       <c r="B1994" t="n">
@@ -20271,7 +20370,7 @@
     <row r="1995">
       <c r="A1995" t="inlineStr">
         <is>
-          <t>392B</t>
+          <t>3817C</t>
         </is>
       </c>
       <c r="B1995" t="n">
@@ -20281,7 +20380,7 @@
     <row r="1996">
       <c r="A1996" t="inlineStr">
         <is>
-          <t>392BH</t>
+          <t>392B</t>
         </is>
       </c>
       <c r="B1996" t="n">
@@ -20291,27 +20390,27 @@
     <row r="1997">
       <c r="A1997" t="inlineStr">
         <is>
-          <t>46098</t>
+          <t>392BH</t>
         </is>
       </c>
       <c r="B1997" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1998">
       <c r="A1998" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="B1998" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1999">
       <c r="A1999" t="inlineStr">
         <is>
-          <t>B2993</t>
+          <t>815</t>
         </is>
       </c>
       <c r="B1999" t="n">
@@ -20321,67 +20420,67 @@
     <row r="2000">
       <c r="A2000" t="inlineStr">
         <is>
-          <t>BCL</t>
+          <t>B2993</t>
         </is>
       </c>
       <c r="B2000" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2001">
       <c r="A2001" t="inlineStr">
         <is>
-          <t>BOBA</t>
+          <t>BCL</t>
         </is>
       </c>
       <c r="B2001" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2002">
       <c r="A2002" t="inlineStr">
         <is>
-          <t>BSA</t>
+          <t>BOBA</t>
         </is>
       </c>
       <c r="B2002" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2003">
       <c r="A2003" t="inlineStr">
         <is>
-          <t>BST</t>
+          <t>BSA</t>
         </is>
       </c>
       <c r="B2003" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2004">
       <c r="A2004" t="inlineStr">
         <is>
-          <t>BTR</t>
+          <t>BST</t>
         </is>
       </c>
       <c r="B2004" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2005">
       <c r="A2005" t="inlineStr">
         <is>
-          <t>CG188L</t>
+          <t>BTR</t>
         </is>
       </c>
       <c r="B2005" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2006">
       <c r="A2006" t="inlineStr">
         <is>
-          <t>CG188S</t>
+          <t>CG188L</t>
         </is>
       </c>
       <c r="B2006" t="n">
@@ -20391,7 +20490,7 @@
     <row r="2007">
       <c r="A2007" t="inlineStr">
         <is>
-          <t>CG189L</t>
+          <t>CG188S</t>
         </is>
       </c>
       <c r="B2007" t="n">
@@ -20401,54 +20500,57 @@
     <row r="2008">
       <c r="A2008" t="inlineStr">
         <is>
-          <t>CUBQ</t>
+          <t>CG189L</t>
         </is>
       </c>
       <c r="B2008" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2009">
       <c r="A2009" t="inlineStr">
         <is>
-          <t>K3511HC</t>
+          <t>CUBQ</t>
         </is>
       </c>
       <c r="B2009" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2010">
       <c r="A2010" t="inlineStr">
         <is>
-          <t>K3513C</t>
+          <t>K3511HC</t>
         </is>
       </c>
       <c r="B2010" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2011">
       <c r="A2011" t="inlineStr">
         <is>
-          <t>KB510</t>
+          <t>K3513C</t>
         </is>
       </c>
       <c r="B2011" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2012">
       <c r="A2012" t="inlineStr">
         <is>
-          <t>TRB1A</t>
-        </is>
+          <t>KB510</t>
+        </is>
+      </c>
+      <c r="B2012" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2013">
       <c r="A2013" t="inlineStr">
         <is>
-          <t>TRB6L</t>
+          <t>TRB1A</t>
         </is>
       </c>
       <c r="B2013" t="n">
@@ -20458,7 +20560,7 @@
     <row r="2014">
       <c r="A2014" t="inlineStr">
         <is>
-          <t>TRB6S</t>
+          <t>TRB6L</t>
         </is>
       </c>
       <c r="B2014" t="n">
@@ -20468,7 +20570,7 @@
     <row r="2015">
       <c r="A2015" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>TRB6S</t>
         </is>
       </c>
       <c r="B2015" t="n">
@@ -20478,7 +20580,7 @@
     <row r="2016">
       <c r="A2016" t="inlineStr">
         <is>
-          <t>103EX</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B2016" t="n">
@@ -20488,7 +20590,7 @@
     <row r="2017">
       <c r="A2017" t="inlineStr">
         <is>
-          <t>110H</t>
+          <t>103EX</t>
         </is>
       </c>
       <c r="B2017" t="n">
@@ -20498,7 +20600,7 @@
     <row r="2018">
       <c r="A2018" t="inlineStr">
         <is>
-          <t>122F</t>
+          <t>110H</t>
         </is>
       </c>
       <c r="B2018" t="n">
@@ -20508,7 +20610,7 @@
     <row r="2019">
       <c r="A2019" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>122F</t>
         </is>
       </c>
       <c r="B2019" t="n">
@@ -20518,27 +20620,27 @@
     <row r="2020">
       <c r="A2020" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="B2020" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2021">
       <c r="A2021" t="inlineStr">
         <is>
-          <t>1290S</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B2021" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2022">
       <c r="A2022" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>1290S</t>
         </is>
       </c>
       <c r="B2022" t="n">
@@ -20548,7 +20650,7 @@
     <row r="2023">
       <c r="A2023" t="inlineStr">
         <is>
-          <t>1400BEX</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B2023" t="n">
@@ -20558,7 +20660,7 @@
     <row r="2024">
       <c r="A2024" t="inlineStr">
         <is>
-          <t>1530C</t>
+          <t>1400BEX</t>
         </is>
       </c>
       <c r="B2024" t="n">
@@ -20568,7 +20670,7 @@
     <row r="2025">
       <c r="A2025" t="inlineStr">
         <is>
-          <t>180/37S</t>
+          <t>1530C</t>
         </is>
       </c>
       <c r="B2025" t="n">
@@ -20578,7 +20680,7 @@
     <row r="2026">
       <c r="A2026" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>180/37S</t>
         </is>
       </c>
       <c r="B2026" t="n">
@@ -20588,17 +20690,17 @@
     <row r="2027">
       <c r="A2027" t="inlineStr">
         <is>
-          <t>180S37</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="B2027" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2028">
       <c r="A2028" t="inlineStr">
         <is>
-          <t>190S37</t>
+          <t>180S37</t>
         </is>
       </c>
       <c r="B2028" t="n">
@@ -20608,37 +20710,37 @@
     <row r="2029">
       <c r="A2029" t="inlineStr">
         <is>
-          <t>1BSP</t>
+          <t>190S37</t>
         </is>
       </c>
       <c r="B2029" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2030">
       <c r="A2030" t="inlineStr">
         <is>
-          <t>36B</t>
+          <t>1BSP</t>
         </is>
       </c>
       <c r="B2030" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2031">
       <c r="A2031" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36B</t>
         </is>
       </c>
       <c r="B2031" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2032">
       <c r="A2032" t="inlineStr">
         <is>
-          <t>42A</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B2032" t="n">
@@ -20648,27 +20750,27 @@
     <row r="2033">
       <c r="A2033" t="inlineStr">
         <is>
-          <t>42AF</t>
+          <t>42A</t>
         </is>
       </c>
       <c r="B2033" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>42CO</t>
+          <t>42AF</t>
         </is>
       </c>
       <c r="B2034" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2035">
       <c r="A2035" t="inlineStr">
         <is>
-          <t>50T</t>
+          <t>42CO</t>
         </is>
       </c>
       <c r="B2035" t="n">
@@ -20678,7 +20780,7 @@
     <row r="2036">
       <c r="A2036" t="inlineStr">
         <is>
-          <t>AS300EX</t>
+          <t>50T</t>
         </is>
       </c>
       <c r="B2036" t="n">
@@ -20688,7 +20790,7 @@
     <row r="2037">
       <c r="A2037" t="inlineStr">
         <is>
-          <t>AS651DIR</t>
+          <t>AS300EX</t>
         </is>
       </c>
       <c r="B2037" t="n">
@@ -20698,7 +20800,7 @@
     <row r="2038">
       <c r="A2038" t="inlineStr">
         <is>
-          <t>AS700</t>
+          <t>AS651DIR</t>
         </is>
       </c>
       <c r="B2038" t="n">
@@ -20708,7 +20810,7 @@
     <row r="2039">
       <c r="A2039" t="inlineStr">
         <is>
-          <t>AS710DIR</t>
+          <t>AS700</t>
         </is>
       </c>
       <c r="B2039" t="n">
@@ -20718,7 +20820,7 @@
     <row r="2040">
       <c r="A2040" t="inlineStr">
         <is>
-          <t>AT501DIR</t>
+          <t>AS710DIR</t>
         </is>
       </c>
       <c r="B2040" t="n">
@@ -20728,47 +20830,47 @@
     <row r="2041">
       <c r="A2041" t="inlineStr">
         <is>
-          <t>BH650DIR</t>
+          <t>AT501DIR</t>
         </is>
       </c>
       <c r="B2041" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2042">
       <c r="A2042" t="inlineStr">
         <is>
-          <t>BH651DIR</t>
+          <t>BH650DIR</t>
         </is>
       </c>
       <c r="B2042" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2043">
       <c r="A2043" t="inlineStr">
         <is>
-          <t>BS650DIR</t>
+          <t>BH651DIR</t>
         </is>
       </c>
       <c r="B2043" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2044">
       <c r="A2044" t="inlineStr">
         <is>
-          <t>BUNDYALII</t>
+          <t>BS650DIR</t>
         </is>
       </c>
       <c r="B2044" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2045">
       <c r="A2045" t="inlineStr">
         <is>
-          <t>CBS280RS</t>
+          <t>BUNDYALII</t>
         </is>
       </c>
       <c r="B2045" t="n">
@@ -20778,7 +20880,7 @@
     <row r="2046">
       <c r="A2046" t="inlineStr">
         <is>
-          <t>CL211</t>
+          <t>CBS280RS</t>
         </is>
       </c>
       <c r="B2046" t="n">
@@ -20788,27 +20890,27 @@
     <row r="2047">
       <c r="A2047" t="inlineStr">
         <is>
-          <t>CL501DIR</t>
+          <t>CL211</t>
         </is>
       </c>
       <c r="B2047" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2048">
       <c r="A2048" t="inlineStr">
         <is>
-          <t>CL700</t>
+          <t>CL501DIR</t>
         </is>
       </c>
       <c r="B2048" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2049">
       <c r="A2049" t="inlineStr">
         <is>
-          <t>CL710DIR</t>
+          <t>CL700</t>
         </is>
       </c>
       <c r="B2049" t="n">
@@ -20818,7 +20920,7 @@
     <row r="2050">
       <c r="A2050" t="inlineStr">
         <is>
-          <t>CLSM</t>
+          <t>CL710DIR</t>
         </is>
       </c>
       <c r="B2050" t="n">
@@ -20828,27 +20930,27 @@
     <row r="2051">
       <c r="A2051" t="inlineStr">
         <is>
-          <t>CR651DIR</t>
+          <t>CLSM</t>
         </is>
       </c>
       <c r="B2051" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2052">
       <c r="A2052" t="inlineStr">
         <is>
-          <t>CR651SDIR</t>
+          <t>CR651DIR</t>
         </is>
       </c>
       <c r="B2052" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2053">
       <c r="A2053" t="inlineStr">
         <is>
-          <t>CR710SDIR</t>
+          <t>CR651SDIR</t>
         </is>
       </c>
       <c r="B2053" t="n">
@@ -20858,7 +20960,7 @@
     <row r="2054">
       <c r="A2054" t="inlineStr">
         <is>
-          <t>EP655DIR</t>
+          <t>CR710SDIR</t>
         </is>
       </c>
       <c r="B2054" t="n">
@@ -20868,17 +20970,17 @@
     <row r="2055">
       <c r="A2055" t="inlineStr">
         <is>
-          <t>FH501DIR</t>
+          <t>EP655DIR</t>
         </is>
       </c>
       <c r="B2055" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2056">
       <c r="A2056" t="inlineStr">
         <is>
-          <t>FH600DIR</t>
+          <t>FH501DIR</t>
         </is>
       </c>
       <c r="B2056" t="n">
@@ -20888,17 +20990,17 @@
     <row r="2057">
       <c r="A2057" t="inlineStr">
         <is>
-          <t>FL700DIR</t>
+          <t>FH600DIR</t>
         </is>
       </c>
       <c r="B2057" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2058">
       <c r="A2058" t="inlineStr">
         <is>
-          <t>FL700RI</t>
+          <t>FL700DIR</t>
         </is>
       </c>
       <c r="B2058" t="n">
@@ -20908,7 +21010,7 @@
     <row r="2059">
       <c r="A2059" t="inlineStr">
         <is>
-          <t>FL710DIR</t>
+          <t>FL700RI</t>
         </is>
       </c>
       <c r="B2059" t="n">
@@ -20918,7 +21020,7 @@
     <row r="2060">
       <c r="A2060" t="inlineStr">
         <is>
-          <t>FL710EDIR</t>
+          <t>FL710DIR</t>
         </is>
       </c>
       <c r="B2060" t="n">
@@ -20928,7 +21030,7 @@
     <row r="2061">
       <c r="A2061" t="inlineStr">
         <is>
-          <t>FL710RIDIR</t>
+          <t>FL710EDIR</t>
         </is>
       </c>
       <c r="B2061" t="n">
@@ -20938,7 +21040,7 @@
     <row r="2062">
       <c r="A2062" t="inlineStr">
         <is>
-          <t>PARIS</t>
+          <t>FL710RIDIR</t>
         </is>
       </c>
       <c r="B2062" t="n">
@@ -20948,7 +21050,7 @@
     <row r="2063">
       <c r="A2063" t="inlineStr">
         <is>
-          <t>PBONE1BK</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="B2063" t="n">
@@ -20958,7 +21060,7 @@
     <row r="2064">
       <c r="A2064" t="inlineStr">
         <is>
-          <t>PBONE1G</t>
+          <t>PBONE1BK</t>
         </is>
       </c>
       <c r="B2064" t="n">
@@ -20968,34 +21070,37 @@
     <row r="2065">
       <c r="A2065" t="inlineStr">
         <is>
-          <t>PBONE1R</t>
+          <t>PBONE1G</t>
         </is>
       </c>
       <c r="B2065" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2066">
       <c r="A2066" t="inlineStr">
         <is>
-          <t>PBONE1W</t>
-        </is>
+          <t>PBONE1R</t>
+        </is>
+      </c>
+      <c r="B2066" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="2067">
       <c r="A2067" t="inlineStr">
         <is>
-          <t>PBONE1Y</t>
+          <t>PBONE1W</t>
         </is>
       </c>
       <c r="B2067" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2068">
       <c r="A2068" t="inlineStr">
         <is>
-          <t>PC710DIR</t>
+          <t>PBONE1Y</t>
         </is>
       </c>
       <c r="B2068" t="n">
@@ -21005,17 +21110,17 @@
     <row r="2069">
       <c r="A2069" t="inlineStr">
         <is>
-          <t>SATE</t>
+          <t>PC710DIR</t>
         </is>
       </c>
       <c r="B2069" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2070">
       <c r="A2070" t="inlineStr">
         <is>
-          <t>SS650DIR</t>
+          <t>SATE</t>
         </is>
       </c>
       <c r="B2070" t="n">
@@ -21025,7 +21130,7 @@
     <row r="2071">
       <c r="A2071" t="inlineStr">
         <is>
-          <t>TB503BDIR</t>
+          <t>SS650DIR</t>
         </is>
       </c>
       <c r="B2071" t="n">
@@ -21035,7 +21140,7 @@
     <row r="2072">
       <c r="A2072" t="inlineStr">
         <is>
-          <t>TB600</t>
+          <t>TB503BDIR</t>
         </is>
       </c>
       <c r="B2072" t="n">
@@ -21045,7 +21150,7 @@
     <row r="2073">
       <c r="A2073" t="inlineStr">
         <is>
-          <t>TR200</t>
+          <t>TB600</t>
         </is>
       </c>
       <c r="B2073" t="n">
@@ -21055,17 +21160,17 @@
     <row r="2074">
       <c r="A2074" t="inlineStr">
         <is>
-          <t>TR300H</t>
+          <t>TR200</t>
         </is>
       </c>
       <c r="B2074" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2075">
       <c r="A2075" t="inlineStr">
         <is>
-          <t>TR300HS</t>
+          <t>TR300H</t>
         </is>
       </c>
       <c r="B2075" t="n">
@@ -21075,37 +21180,37 @@
     <row r="2076">
       <c r="A2076" t="inlineStr">
         <is>
-          <t>TR300HXS</t>
+          <t>TR300HS</t>
         </is>
       </c>
       <c r="B2076" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2077">
       <c r="A2077" t="inlineStr">
         <is>
-          <t>TR500DIR</t>
+          <t>TR300HXS</t>
         </is>
       </c>
       <c r="B2077" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2078">
       <c r="A2078" t="inlineStr">
         <is>
-          <t>TR500S</t>
+          <t>TR500DIR</t>
         </is>
       </c>
       <c r="B2078" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2079">
       <c r="A2079" t="inlineStr">
         <is>
-          <t>TR500SDIR</t>
+          <t>TR500S</t>
         </is>
       </c>
       <c r="B2079" t="n">
@@ -21115,7 +21220,7 @@
     <row r="2080">
       <c r="A2080" t="inlineStr">
         <is>
-          <t>TR650DIR</t>
+          <t>TR500SDIR</t>
         </is>
       </c>
       <c r="B2080" t="n">
@@ -21125,7 +21230,7 @@
     <row r="2081">
       <c r="A2081" t="inlineStr">
         <is>
-          <t>TR655DIR</t>
+          <t>TR650DIR</t>
         </is>
       </c>
       <c r="B2081" t="n">
@@ -21135,7 +21240,7 @@
     <row r="2082">
       <c r="A2082" t="inlineStr">
         <is>
-          <t>TR700</t>
+          <t>TR655DIR</t>
         </is>
       </c>
       <c r="B2082" t="n">
@@ -21145,7 +21250,7 @@
     <row r="2083">
       <c r="A2083" t="inlineStr">
         <is>
-          <t>TR710DIR</t>
+          <t>TR700</t>
         </is>
       </c>
       <c r="B2083" t="n">
@@ -21155,7 +21260,7 @@
     <row r="2084">
       <c r="A2084" t="inlineStr">
         <is>
-          <t>TR710SDIR</t>
+          <t>TR710DIR</t>
         </is>
       </c>
       <c r="B2084" t="n">
@@ -21165,7 +21270,7 @@
     <row r="2085">
       <c r="A2085" t="inlineStr">
         <is>
-          <t>TS710DIR</t>
+          <t>TR710SDIR</t>
         </is>
       </c>
       <c r="B2085" t="n">
@@ -21175,7 +21280,7 @@
     <row r="2086">
       <c r="A2086" t="inlineStr">
         <is>
-          <t>VBS1SW2</t>
+          <t>TS710DIR</t>
         </is>
       </c>
       <c r="B2086" t="n">
@@ -21185,7 +21290,7 @@
     <row r="2087">
       <c r="A2087" t="inlineStr">
         <is>
-          <t>VT501DIR</t>
+          <t>VBS1SW2</t>
         </is>
       </c>
       <c r="B2087" t="n">
@@ -21195,27 +21300,27 @@
     <row r="2088">
       <c r="A2088" t="inlineStr">
         <is>
-          <t>ARCOCONT</t>
+          <t>VT501DIR</t>
         </is>
       </c>
       <c r="B2088" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2089">
       <c r="A2089" t="inlineStr">
         <is>
-          <t>ARCOSALEMA</t>
+          <t>ARCOCONT</t>
         </is>
       </c>
       <c r="B2089" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2090">
       <c r="A2090" t="inlineStr">
         <is>
-          <t>FL542</t>
+          <t>ARCOSALEMA</t>
         </is>
       </c>
       <c r="B2090" t="n">
@@ -21225,7 +21330,7 @@
     <row r="2091">
       <c r="A2091" t="inlineStr">
         <is>
-          <t>FLB760 4/4</t>
+          <t>FL542</t>
         </is>
       </c>
       <c r="B2091" t="n">
@@ -21235,7 +21340,7 @@
     <row r="2092">
       <c r="A2092" t="inlineStr">
         <is>
-          <t>DBS100 1/2</t>
+          <t>FLB760 4/4</t>
         </is>
       </c>
       <c r="B2092" t="n">
@@ -21245,7 +21350,7 @@
     <row r="2093">
       <c r="A2093" t="inlineStr">
         <is>
-          <t>DBS100 3/4</t>
+          <t>DBS100 1/2</t>
         </is>
       </c>
       <c r="B2093" t="n">
@@ -21255,67 +21360,67 @@
     <row r="2094">
       <c r="A2094" t="inlineStr">
         <is>
-          <t>DBS100 4/4</t>
+          <t>DBS100 3/4</t>
         </is>
       </c>
       <c r="B2094" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2095">
       <c r="A2095" t="inlineStr">
         <is>
-          <t>DCE100 1/2</t>
+          <t>DBS100 4/4</t>
         </is>
       </c>
       <c r="B2095" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2096">
       <c r="A2096" t="inlineStr">
         <is>
-          <t>DCE100 3/4</t>
+          <t>DCE100 1/2</t>
         </is>
       </c>
       <c r="B2096" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2097">
       <c r="A2097" t="inlineStr">
         <is>
-          <t>DCE100 4/4</t>
+          <t>DCE100 3/4</t>
         </is>
       </c>
       <c r="B2097" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2098">
       <c r="A2098" t="inlineStr">
         <is>
-          <t>DCE101 4/4</t>
+          <t>DCE100 4/4</t>
         </is>
       </c>
       <c r="B2098" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2099">
       <c r="A2099" t="inlineStr">
         <is>
-          <t>DVA106 4/4</t>
+          <t>DCE101 4/4</t>
         </is>
       </c>
       <c r="B2099" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2100">
       <c r="A2100" t="inlineStr">
         <is>
-          <t>DVN102 1/4</t>
+          <t>DVA106 4/4</t>
         </is>
       </c>
       <c r="B2100" t="n">
@@ -21325,17 +21430,17 @@
     <row r="2101">
       <c r="A2101" t="inlineStr">
         <is>
-          <t>DVN102 1/8</t>
+          <t>DVN102 1/4</t>
         </is>
       </c>
       <c r="B2101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2102">
       <c r="A2102" t="inlineStr">
         <is>
-          <t>DVN102 3/4</t>
+          <t>DVN102 1/8</t>
         </is>
       </c>
       <c r="B2102" t="n">
@@ -21345,27 +21450,27 @@
     <row r="2103">
       <c r="A2103" t="inlineStr">
         <is>
-          <t>DVN102 4/4</t>
+          <t>DVN102 3/4</t>
         </is>
       </c>
       <c r="B2103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2104">
       <c r="A2104" t="inlineStr">
         <is>
-          <t>DVN306 4/4</t>
+          <t>DVN102 4/4</t>
         </is>
       </c>
       <c r="B2104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2105">
       <c r="A2105" t="inlineStr">
         <is>
-          <t>FL008L 4/4</t>
+          <t>DVN306 4/4</t>
         </is>
       </c>
       <c r="B2105" t="n">
@@ -21375,27 +21480,27 @@
     <row r="2106">
       <c r="A2106" t="inlineStr">
         <is>
-          <t>FL016 4/4</t>
+          <t>FL008L 4/4</t>
         </is>
       </c>
       <c r="B2106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2107">
       <c r="A2107" t="inlineStr">
         <is>
-          <t>FL08-1L3/4</t>
+          <t>FL016 4/4</t>
         </is>
       </c>
       <c r="B2107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2108">
       <c r="A2108" t="inlineStr">
         <is>
-          <t>FL08-2L1/2</t>
+          <t>FL08-1L3/4</t>
         </is>
       </c>
       <c r="B2108" t="n">
@@ -21405,7 +21510,7 @@
     <row r="2109">
       <c r="A2109" t="inlineStr">
         <is>
-          <t>FL08-3L1/4</t>
+          <t>FL08-2L1/2</t>
         </is>
       </c>
       <c r="B2109" t="n">
@@ -21415,7 +21520,7 @@
     <row r="2110">
       <c r="A2110" t="inlineStr">
         <is>
-          <t>FL08-8L1/8</t>
+          <t>FL08-3L1/4</t>
         </is>
       </c>
       <c r="B2110" t="n">
@@ -21425,47 +21530,47 @@
     <row r="2111">
       <c r="A2111" t="inlineStr">
         <is>
-          <t>FL406E16</t>
+          <t>FL08-8L1/8</t>
         </is>
       </c>
       <c r="B2111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2112">
       <c r="A2112" t="inlineStr">
         <is>
-          <t>FL760R 1/2</t>
+          <t>FL406E16</t>
         </is>
       </c>
       <c r="B2112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2113">
       <c r="A2113" t="inlineStr">
         <is>
-          <t>FL760R4/4</t>
+          <t>FL760R 1/2</t>
         </is>
       </c>
       <c r="B2113" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2114">
       <c r="A2114" t="inlineStr">
         <is>
-          <t>MB040L</t>
+          <t>FL760R4/4</t>
         </is>
       </c>
       <c r="B2114" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2115">
       <c r="A2115" t="inlineStr">
         <is>
-          <t>STEINER4/4</t>
+          <t>MB040L</t>
         </is>
       </c>
       <c r="B2115" t="n">
@@ -21475,7 +21580,7 @@
     <row r="2116">
       <c r="A2116" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>STEINER4/4</t>
         </is>
       </c>
       <c r="B2116" t="n">
@@ -21485,17 +21590,17 @@
     <row r="2117">
       <c r="A2117" t="inlineStr">
         <is>
-          <t>ARCO33</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B2117" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2118">
       <c r="A2118" t="inlineStr">
         <is>
-          <t>ARCO37</t>
+          <t>ARCO33</t>
         </is>
       </c>
       <c r="B2118" t="n">
@@ -21505,7 +21610,7 @@
     <row r="2119">
       <c r="A2119" t="inlineStr">
         <is>
-          <t>ARCO38</t>
+          <t>ARCO37</t>
         </is>
       </c>
       <c r="B2119" t="n">
@@ -21515,17 +21620,17 @@
     <row r="2120">
       <c r="A2120" t="inlineStr">
         <is>
-          <t>ESTU4/4</t>
+          <t>ARCO38</t>
         </is>
       </c>
       <c r="B2120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2121">
       <c r="A2121" t="inlineStr">
         <is>
-          <t>ESTUVO10F</t>
+          <t>ESTU4/4</t>
         </is>
       </c>
       <c r="B2121" t="n">
@@ -21535,7 +21640,7 @@
     <row r="2122">
       <c r="A2122" t="inlineStr">
         <is>
-          <t>HD3C</t>
+          <t>ESTUVO10F</t>
         </is>
       </c>
       <c r="B2122" t="n">
@@ -21545,27 +21650,27 @@
     <row r="2123">
       <c r="A2123" t="inlineStr">
         <is>
-          <t>ME-MAJOR5</t>
+          <t>HD3C</t>
         </is>
       </c>
       <c r="B2123" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2124">
       <c r="A2124" t="inlineStr">
         <is>
-          <t>220-1/4</t>
+          <t>ME-MAJOR5</t>
         </is>
       </c>
       <c r="B2124" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2125">
       <c r="A2125" t="inlineStr">
         <is>
-          <t>220-1/8</t>
+          <t>220-1/4</t>
         </is>
       </c>
       <c r="B2125" t="n">
@@ -21575,7 +21680,7 @@
     <row r="2126">
       <c r="A2126" t="inlineStr">
         <is>
-          <t>540-4/4</t>
+          <t>220-1/8</t>
         </is>
       </c>
       <c r="B2126" t="n">
@@ -21585,7 +21690,7 @@
     <row r="2127">
       <c r="A2127" t="inlineStr">
         <is>
-          <t>SBI15 5JB</t>
+          <t>540-4/4</t>
         </is>
       </c>
       <c r="B2127" t="n">
@@ -21595,7 +21700,7 @@
     <row r="2128">
       <c r="A2128" t="inlineStr">
         <is>
-          <t>SCG 5CE</t>
+          <t>SBI15 5JB</t>
         </is>
       </c>
       <c r="B2128" t="n">
@@ -21605,7 +21710,7 @@
     <row r="2129">
       <c r="A2129" t="inlineStr">
         <is>
-          <t>SG3B</t>
+          <t>SCG 5CE</t>
         </is>
       </c>
       <c r="B2129" t="n">
@@ -21615,7 +21720,7 @@
     <row r="2130">
       <c r="A2130" t="inlineStr">
         <is>
-          <t>SG3S</t>
+          <t>SG3B</t>
         </is>
       </c>
       <c r="B2130" t="n">
@@ -21625,7 +21730,7 @@
     <row r="2131">
       <c r="A2131" t="inlineStr">
         <is>
-          <t>SJB20BK</t>
+          <t>SG3S</t>
         </is>
       </c>
       <c r="B2131" t="n">
@@ -21635,7 +21740,7 @@
     <row r="2132">
       <c r="A2132" t="inlineStr">
         <is>
-          <t>SJB20SB</t>
+          <t>SJB20BK</t>
         </is>
       </c>
       <c r="B2132" t="n">
@@ -21645,14 +21750,17 @@
     <row r="2133">
       <c r="A2133" t="inlineStr">
         <is>
-          <t>SNG3</t>
-        </is>
+          <t>SJB20SB</t>
+        </is>
+      </c>
+      <c r="B2133" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2134">
       <c r="A2134" t="inlineStr">
         <is>
-          <t>SSG300</t>
+          <t>SNG3</t>
         </is>
       </c>
       <c r="B2134" t="n">
@@ -21662,7 +21770,7 @@
     <row r="2135">
       <c r="A2135" t="inlineStr">
         <is>
-          <t>SST20 CS</t>
+          <t>SSG300</t>
         </is>
       </c>
       <c r="B2135" t="n">
@@ -21672,7 +21780,7 @@
     <row r="2136">
       <c r="A2136" t="inlineStr">
         <is>
-          <t>SST20 SB</t>
+          <t>SST20 CS</t>
         </is>
       </c>
       <c r="B2136" t="n">
@@ -21682,27 +21790,27 @@
     <row r="2137">
       <c r="A2137" t="inlineStr">
         <is>
-          <t>STE50</t>
+          <t>SST20 SB</t>
         </is>
       </c>
       <c r="B2137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2138">
       <c r="A2138" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>STE50</t>
         </is>
       </c>
       <c r="B2138" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2139">
       <c r="A2139" t="inlineStr">
         <is>
-          <t>1072 A</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="B2139" t="n">
@@ -21712,7 +21820,7 @@
     <row r="2140">
       <c r="A2140" t="inlineStr">
         <is>
-          <t>1072 C</t>
+          <t>1072 A</t>
         </is>
       </c>
       <c r="B2140" t="n">
@@ -21722,17 +21830,17 @@
     <row r="2141">
       <c r="A2141" t="inlineStr">
         <is>
-          <t>1072 D</t>
+          <t>1072 C</t>
         </is>
       </c>
       <c r="B2141" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>1072 E</t>
+          <t>1072 D</t>
         </is>
       </c>
       <c r="B2142" t="n">
@@ -21742,7 +21850,7 @@
     <row r="2143">
       <c r="A2143" t="inlineStr">
         <is>
-          <t>1072 F</t>
+          <t>1072 E</t>
         </is>
       </c>
       <c r="B2143" t="n">
@@ -21752,7 +21860,7 @@
     <row r="2144">
       <c r="A2144" t="inlineStr">
         <is>
-          <t>1072 G</t>
+          <t>1072 F</t>
         </is>
       </c>
       <c r="B2144" t="n">
@@ -21762,17 +21870,17 @@
     <row r="2145">
       <c r="A2145" t="inlineStr">
         <is>
-          <t>C20 A</t>
+          <t>1072 G</t>
         </is>
       </c>
       <c r="B2145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2146">
       <c r="A2146" t="inlineStr">
         <is>
-          <t>C20 C</t>
+          <t>C20 A</t>
         </is>
       </c>
       <c r="B2146" t="n">
@@ -21782,27 +21890,27 @@
     <row r="2147">
       <c r="A2147" t="inlineStr">
         <is>
-          <t>C20 D</t>
+          <t>C20 C</t>
         </is>
       </c>
       <c r="B2147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2148">
       <c r="A2148" t="inlineStr">
         <is>
-          <t>C20 E</t>
+          <t>C20 D</t>
         </is>
       </c>
       <c r="B2148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2149">
       <c r="A2149" t="inlineStr">
         <is>
-          <t>C20 F</t>
+          <t>C20 E</t>
         </is>
       </c>
       <c r="B2149" t="n">
@@ -21812,37 +21920,37 @@
     <row r="2150">
       <c r="A2150" t="inlineStr">
         <is>
-          <t>C20 G</t>
+          <t>C20 F</t>
         </is>
       </c>
       <c r="B2150" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2151">
       <c r="A2151" t="inlineStr">
         <is>
-          <t>EZR20</t>
+          <t>C20 G</t>
         </is>
       </c>
       <c r="B2151" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2152">
       <c r="A2152" t="inlineStr">
         <is>
-          <t>EZR20AL</t>
+          <t>EZR20</t>
         </is>
       </c>
       <c r="B2152" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2153">
       <c r="A2153" t="inlineStr">
         <is>
-          <t>EZR20BS</t>
+          <t>EZR20AL</t>
         </is>
       </c>
       <c r="B2153" t="n">
@@ -21852,17 +21960,17 @@
     <row r="2154">
       <c r="A2154" t="inlineStr">
         <is>
-          <t>M20</t>
+          <t>EZR20BS</t>
         </is>
       </c>
       <c r="B2154" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2155">
       <c r="A2155" t="inlineStr">
         <is>
-          <t>M20 A</t>
+          <t>M20</t>
         </is>
       </c>
       <c r="B2155" t="n">
@@ -21872,7 +21980,7 @@
     <row r="2156">
       <c r="A2156" t="inlineStr">
         <is>
-          <t>M20 C</t>
+          <t>M20 A</t>
         </is>
       </c>
       <c r="B2156" t="n">
@@ -21882,7 +21990,7 @@
     <row r="2157">
       <c r="A2157" t="inlineStr">
         <is>
-          <t>M20 D</t>
+          <t>M20 C</t>
         </is>
       </c>
       <c r="B2157" t="n">
@@ -21892,17 +22000,17 @@
     <row r="2158">
       <c r="A2158" t="inlineStr">
         <is>
-          <t>M20 E</t>
+          <t>M20 D</t>
         </is>
       </c>
       <c r="B2158" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2159">
       <c r="A2159" t="inlineStr">
         <is>
-          <t>M20 F</t>
+          <t>M20 E</t>
         </is>
       </c>
       <c r="B2159" t="n">
@@ -21912,7 +22020,7 @@
     <row r="2160">
       <c r="A2160" t="inlineStr">
         <is>
-          <t>M20 G</t>
+          <t>M20 F</t>
         </is>
       </c>
       <c r="B2160" t="n">
@@ -21922,27 +22030,27 @@
     <row r="2161">
       <c r="A2161" t="inlineStr">
         <is>
-          <t>M20 LP</t>
+          <t>M20 G</t>
         </is>
       </c>
       <c r="B2161" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2162">
       <c r="A2162" t="inlineStr">
         <is>
-          <t>M20S A</t>
+          <t>M20 LP</t>
         </is>
       </c>
       <c r="B2162" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2163">
       <c r="A2163" t="inlineStr">
         <is>
-          <t>M20S C</t>
+          <t>M20S A</t>
         </is>
       </c>
       <c r="B2163" t="n">
@@ -21952,27 +22060,27 @@
     <row r="2164">
       <c r="A2164" t="inlineStr">
         <is>
-          <t>M20S D</t>
+          <t>M20S C</t>
         </is>
       </c>
       <c r="B2164" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2165">
       <c r="A2165" t="inlineStr">
         <is>
-          <t>M20S E</t>
+          <t>M20S D</t>
         </is>
       </c>
       <c r="B2165" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2166">
       <c r="A2166" t="inlineStr">
         <is>
-          <t>M20S F</t>
+          <t>M20S E</t>
         </is>
       </c>
       <c r="B2166" t="n">
@@ -21982,7 +22090,7 @@
     <row r="2167">
       <c r="A2167" t="inlineStr">
         <is>
-          <t>M20S G</t>
+          <t>M20S F</t>
         </is>
       </c>
       <c r="B2167" t="n">
@@ -21992,17 +22100,17 @@
     <row r="2168">
       <c r="A2168" t="inlineStr">
         <is>
-          <t>M37C</t>
+          <t>M20S G</t>
         </is>
       </c>
       <c r="B2168" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2169">
       <c r="A2169" t="inlineStr">
         <is>
-          <t>M37C PLUS</t>
+          <t>M37C</t>
         </is>
       </c>
       <c r="B2169" t="n">
@@ -22012,47 +22120,47 @@
     <row r="2170">
       <c r="A2170" t="inlineStr">
         <is>
-          <t>MR200 A</t>
+          <t>M37C PLUS</t>
         </is>
       </c>
       <c r="B2170" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2171">
       <c r="A2171" t="inlineStr">
         <is>
-          <t>MR200 B</t>
+          <t>MR200 A</t>
         </is>
       </c>
       <c r="B2171" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2172">
       <c r="A2172" t="inlineStr">
         <is>
-          <t>MR200 C</t>
+          <t>MR200 B</t>
         </is>
       </c>
       <c r="B2172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2173">
       <c r="A2173" t="inlineStr">
         <is>
-          <t>MR200 D</t>
+          <t>MR200 C</t>
         </is>
       </c>
       <c r="B2173" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2174">
       <c r="A2174" t="inlineStr">
         <is>
-          <t>MR200 E</t>
+          <t>MR200 D</t>
         </is>
       </c>
       <c r="B2174" t="n">
@@ -22062,7 +22170,7 @@
     <row r="2175">
       <c r="A2175" t="inlineStr">
         <is>
-          <t>MR200 F</t>
+          <t>MR200 E</t>
         </is>
       </c>
       <c r="B2175" t="n">
@@ -22072,7 +22180,7 @@
     <row r="2176">
       <c r="A2176" t="inlineStr">
         <is>
-          <t>MR200 G</t>
+          <t>MR200 F</t>
         </is>
       </c>
       <c r="B2176" t="n">
@@ -22082,17 +22190,17 @@
     <row r="2177">
       <c r="A2177" t="inlineStr">
         <is>
-          <t>MR250</t>
+          <t>MR200 G</t>
         </is>
       </c>
       <c r="B2177" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2178">
       <c r="A2178" t="inlineStr">
         <is>
-          <t>MR250 E</t>
+          <t>MR250</t>
         </is>
       </c>
       <c r="B2178" t="n">
@@ -22102,7 +22210,7 @@
     <row r="2179">
       <c r="A2179" t="inlineStr">
         <is>
-          <t>MR300 E</t>
+          <t>MR250 E</t>
         </is>
       </c>
       <c r="B2179" t="n">
@@ -22112,7 +22220,7 @@
     <row r="2180">
       <c r="A2180" t="inlineStr">
         <is>
-          <t>MR300 G</t>
+          <t>MR300 E</t>
         </is>
       </c>
       <c r="B2180" t="n">
@@ -22122,17 +22230,17 @@
     <row r="2181">
       <c r="A2181" t="inlineStr">
         <is>
-          <t>MR350 A</t>
+          <t>MR300 G</t>
         </is>
       </c>
       <c r="B2181" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2182">
       <c r="A2182" t="inlineStr">
         <is>
-          <t>MR350 B</t>
+          <t>MR350 A</t>
         </is>
       </c>
       <c r="B2182" t="n">
@@ -22142,37 +22250,37 @@
     <row r="2183">
       <c r="A2183" t="inlineStr">
         <is>
-          <t>MR350 C</t>
+          <t>MR350 B</t>
         </is>
       </c>
       <c r="B2183" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2184">
       <c r="A2184" t="inlineStr">
         <is>
-          <t>MR350 D</t>
+          <t>MR350 C</t>
         </is>
       </c>
       <c r="B2184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2185">
       <c r="A2185" t="inlineStr">
         <is>
-          <t>MR350 E</t>
+          <t>MR350 D</t>
         </is>
       </c>
       <c r="B2185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2186">
       <c r="A2186" t="inlineStr">
         <is>
-          <t>MR350 F</t>
+          <t>MR350 E</t>
         </is>
       </c>
       <c r="B2186" t="n">
@@ -22182,27 +22290,27 @@
     <row r="2187">
       <c r="A2187" t="inlineStr">
         <is>
-          <t>MR350 G</t>
+          <t>MR350 F</t>
         </is>
       </c>
       <c r="B2187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2188">
       <c r="A2188" t="inlineStr">
         <is>
-          <t>MR500 E</t>
+          <t>MR350 G</t>
         </is>
       </c>
       <c r="B2188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2189">
       <c r="A2189" t="inlineStr">
         <is>
-          <t>MR550</t>
+          <t>MR500 E</t>
         </is>
       </c>
       <c r="B2189" t="n">
@@ -22212,7 +22320,7 @@
     <row r="2190">
       <c r="A2190" t="inlineStr">
         <is>
-          <t>MR550 C</t>
+          <t>MR550</t>
         </is>
       </c>
       <c r="B2190" t="n">
@@ -22222,7 +22330,7 @@
     <row r="2191">
       <c r="A2191" t="inlineStr">
         <is>
-          <t>MR550 E</t>
+          <t>MR550 C</t>
         </is>
       </c>
       <c r="B2191" t="n">
@@ -22232,7 +22340,7 @@
     <row r="2192">
       <c r="A2192" t="inlineStr">
         <is>
-          <t>MR550 G</t>
+          <t>MR550 E</t>
         </is>
       </c>
       <c r="B2192" t="n">
@@ -22242,17 +22350,17 @@
     <row r="2193">
       <c r="A2193" t="inlineStr">
         <is>
-          <t>MX32D</t>
+          <t>MR550 G</t>
         </is>
       </c>
       <c r="B2193" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2194">
       <c r="A2194" t="inlineStr">
         <is>
-          <t>MX37C</t>
+          <t>MX32D</t>
         </is>
       </c>
       <c r="B2194" t="n">
@@ -22262,17 +22370,17 @@
     <row r="2195">
       <c r="A2195" t="inlineStr">
         <is>
-          <t>P365HCDP</t>
+          <t>MX37C</t>
         </is>
       </c>
       <c r="B2195" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2196">
       <c r="A2196" t="inlineStr">
         <is>
-          <t>PRO37V3</t>
+          <t>P365HCDP</t>
         </is>
       </c>
       <c r="B2196" t="n">
@@ -22282,37 +22390,37 @@
     <row r="2197">
       <c r="A2197" t="inlineStr">
         <is>
-          <t>PRO44H</t>
+          <t>PRO37V3</t>
         </is>
       </c>
       <c r="B2197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2198">
       <c r="A2198" t="inlineStr">
         <is>
-          <t>PRO44HPV2</t>
+          <t>PRO44H</t>
         </is>
       </c>
       <c r="B2198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2199">
       <c r="A2199" t="inlineStr">
         <is>
-          <t>PRO44HV2</t>
+          <t>PRO44HPV2</t>
         </is>
       </c>
       <c r="B2199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2200">
       <c r="A2200" t="inlineStr">
         <is>
-          <t>SC48</t>
+          <t>PRO44HV2</t>
         </is>
       </c>
       <c r="B2200" t="n">
@@ -22322,67 +22430,67 @@
     <row r="2201">
       <c r="A2201" t="inlineStr">
         <is>
-          <t>SC48G</t>
+          <t>SC48</t>
         </is>
       </c>
       <c r="B2201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2202">
       <c r="A2202" t="inlineStr">
         <is>
-          <t>SCX48C</t>
+          <t>SC48G</t>
         </is>
       </c>
       <c r="B2202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2203">
       <c r="A2203" t="inlineStr">
         <is>
-          <t>SCX64C</t>
+          <t>SCX48C</t>
         </is>
       </c>
       <c r="B2203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2204">
       <c r="A2204" t="inlineStr">
         <is>
-          <t>SRG200</t>
+          <t>SCX64C</t>
         </is>
       </c>
       <c r="B2204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2205">
       <c r="A2205" t="inlineStr">
         <is>
-          <t>SRG405</t>
+          <t>SRG200</t>
         </is>
       </c>
       <c r="B2205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2206">
       <c r="A2206" t="inlineStr">
         <is>
-          <t>STUDY32BK</t>
+          <t>SRG405</t>
         </is>
       </c>
       <c r="B2206" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2207">
       <c r="A2207" t="inlineStr">
         <is>
-          <t>STUDY32BL</t>
+          <t>STUDY32BK</t>
         </is>
       </c>
       <c r="B2207" t="n">
@@ -22392,17 +22500,17 @@
     <row r="2208">
       <c r="A2208" t="inlineStr">
         <is>
-          <t>STUDY32PK</t>
+          <t>STUDY32BL</t>
         </is>
       </c>
       <c r="B2208" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2209">
       <c r="A2209" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>STUDY32PK</t>
         </is>
       </c>
       <c r="B2209" t="n">
@@ -22412,7 +22520,7 @@
     <row r="2210">
       <c r="A2210" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="B2210" t="n">
@@ -22422,7 +22530,7 @@
     <row r="2211">
       <c r="A2211" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="B2211" t="n">
@@ -22432,27 +22540,27 @@
     <row r="2212">
       <c r="A2212" t="inlineStr">
         <is>
-          <t>SP37</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="B2212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2213">
       <c r="A2213" t="inlineStr">
         <is>
-          <t>SP47</t>
+          <t>SP37</t>
         </is>
       </c>
       <c r="B2213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2214">
       <c r="A2214" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>SP47</t>
         </is>
       </c>
       <c r="B2214" t="n">
@@ -22462,7 +22570,7 @@
     <row r="2215">
       <c r="A2215" t="inlineStr">
         <is>
-          <t>SS100</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="B2215" t="n">
@@ -22472,7 +22580,7 @@
     <row r="2216">
       <c r="A2216" t="inlineStr">
         <is>
-          <t>CL08</t>
+          <t>SS100</t>
         </is>
       </c>
       <c r="B2216" t="n">
@@ -22482,17 +22590,17 @@
     <row r="2217">
       <c r="A2217" t="inlineStr">
         <is>
-          <t>MS200BK</t>
+          <t>CL08</t>
         </is>
       </c>
       <c r="B2217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2218">
       <c r="A2218" t="inlineStr">
         <is>
-          <t>MS205</t>
+          <t>MS200BK</t>
         </is>
       </c>
       <c r="B2218" t="n">
@@ -22502,17 +22610,17 @@
     <row r="2219">
       <c r="A2219" t="inlineStr">
         <is>
-          <t>MS205BK</t>
+          <t>MS205</t>
         </is>
       </c>
       <c r="B2219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2220">
       <c r="A2220" t="inlineStr">
         <is>
-          <t>MS205STBK</t>
+          <t>MS205BK</t>
         </is>
       </c>
       <c r="B2220" t="n">
@@ -22522,7 +22630,7 @@
     <row r="2221">
       <c r="A2221" t="inlineStr">
         <is>
-          <t>RW200</t>
+          <t>MS205STBK</t>
         </is>
       </c>
       <c r="B2221" t="n">
@@ -22532,7 +22640,7 @@
     <row r="2222">
       <c r="A2222" t="inlineStr">
         <is>
-          <t>RW30</t>
+          <t>RW200</t>
         </is>
       </c>
       <c r="B2222" t="n">
@@ -22542,17 +22650,17 @@
     <row r="2223">
       <c r="A2223" t="inlineStr">
         <is>
-          <t>VCH400B</t>
+          <t>RW30</t>
         </is>
       </c>
       <c r="B2223" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2224">
       <c r="A2224" t="inlineStr">
         <is>
-          <t>VCH900B</t>
+          <t>VCH400B</t>
         </is>
       </c>
       <c r="B2224" t="n">
@@ -22562,17 +22670,17 @@
     <row r="2225">
       <c r="A2225" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>VCH900B</t>
         </is>
       </c>
       <c r="B2225" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2226">
       <c r="A2226" t="inlineStr">
         <is>
-          <t>AM1440BNSM</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="B2226" t="n">
@@ -22582,17 +22690,17 @@
     <row r="2227">
       <c r="A2227" t="inlineStr">
         <is>
-          <t>AM1465BNCC</t>
+          <t>AM1440BNSM</t>
         </is>
       </c>
       <c r="B2227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2228">
       <c r="A2228" t="inlineStr">
         <is>
-          <t>BK22BMTT</t>
+          <t>AM1465BNCC</t>
         </is>
       </c>
       <c r="B2228" t="n">
@@ -22602,7 +22710,7 @@
     <row r="2229">
       <c r="A2229" t="inlineStr">
         <is>
-          <t>BST1465BK</t>
+          <t>BK22BMTT</t>
         </is>
       </c>
       <c r="B2229" t="n">
@@ -22612,87 +22720,87 @@
     <row r="2230">
       <c r="A2230" t="inlineStr">
         <is>
-          <t>CA30EN</t>
+          <t>BST1465BK</t>
         </is>
       </c>
       <c r="B2230" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2231">
       <c r="A2231" t="inlineStr">
         <is>
-          <t>CB900AS</t>
+          <t>CA30EN</t>
         </is>
       </c>
       <c r="B2231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2232">
       <c r="A2232" t="inlineStr">
         <is>
-          <t>CB900PS</t>
+          <t>CB900AS</t>
         </is>
       </c>
       <c r="B2232" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2233">
       <c r="A2233" t="inlineStr">
         <is>
-          <t>CB90F</t>
+          <t>CB900PS</t>
         </is>
       </c>
       <c r="B2233" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2234">
       <c r="A2234" t="inlineStr">
         <is>
-          <t>CBA56</t>
+          <t>CB90F</t>
         </is>
       </c>
       <c r="B2234" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2235">
       <c r="A2235" t="inlineStr">
         <is>
-          <t>CBH50</t>
+          <t>CBA56</t>
         </is>
       </c>
       <c r="B2235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2236">
       <c r="A2236" t="inlineStr">
         <is>
-          <t>CC900S</t>
+          <t>CBH50</t>
         </is>
       </c>
       <c r="B2236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2237">
       <c r="A2237" t="inlineStr">
         <is>
-          <t>CJP44CHBK</t>
+          <t>CC900S</t>
         </is>
       </c>
       <c r="B2237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2238">
       <c r="A2238" t="inlineStr">
         <is>
-          <t>CK52KRSICA</t>
+          <t>CJP44CHBK</t>
         </is>
       </c>
       <c r="B2238" t="n">
@@ -22702,7 +22810,7 @@
     <row r="2239">
       <c r="A2239" t="inlineStr">
         <is>
-          <t>CK52KRSISP</t>
+          <t>CK52KRSICA</t>
         </is>
       </c>
       <c r="B2239" t="n">
@@ -22712,7 +22820,7 @@
     <row r="2240">
       <c r="A2240" t="inlineStr">
         <is>
-          <t>CK52KRSMGD</t>
+          <t>CK52KRSISP</t>
         </is>
       </c>
       <c r="B2240" t="n">
@@ -22722,7 +22830,7 @@
     <row r="2241">
       <c r="A2241" t="inlineStr">
         <is>
-          <t>CK52KRSNET</t>
+          <t>CK52KRSMGD</t>
         </is>
       </c>
       <c r="B2241" t="n">
@@ -22732,7 +22840,7 @@
     <row r="2242">
       <c r="A2242" t="inlineStr">
         <is>
-          <t>CL08</t>
+          <t>CK52KRSNET</t>
         </is>
       </c>
       <c r="B2242" t="n">
@@ -22742,7 +22850,7 @@
     <row r="2243">
       <c r="A2243" t="inlineStr">
         <is>
-          <t>CL52KRSBAB</t>
+          <t>CL08</t>
         </is>
       </c>
       <c r="B2243" t="n">
@@ -22752,7 +22860,7 @@
     <row r="2244">
       <c r="A2244" t="inlineStr">
         <is>
-          <t>CL52KRSCFF</t>
+          <t>CL52KRSBAB</t>
         </is>
       </c>
       <c r="B2244" t="n">
@@ -22762,7 +22870,7 @@
     <row r="2245">
       <c r="A2245" t="inlineStr">
         <is>
-          <t>CL52KRSPGH</t>
+          <t>CL52KRSCFF</t>
         </is>
       </c>
       <c r="B2245" t="n">
@@ -22772,7 +22880,7 @@
     <row r="2246">
       <c r="A2246" t="inlineStr">
         <is>
-          <t>CL52KRSTPB</t>
+          <t>CL52KRSPGH</t>
         </is>
       </c>
       <c r="B2246" t="n">
@@ -22782,7 +22890,7 @@
     <row r="2247">
       <c r="A2247" t="inlineStr">
         <is>
-          <t>CL72RSPCLP</t>
+          <t>CL52KRSTPB</t>
         </is>
       </c>
       <c r="B2247" t="n">
@@ -22792,7 +22900,7 @@
     <row r="2248">
       <c r="A2248" t="inlineStr">
         <is>
-          <t>CL72RSPGGP</t>
+          <t>CL72RSPCLP</t>
         </is>
       </c>
       <c r="B2248" t="n">
@@ -22802,7 +22910,7 @@
     <row r="2249">
       <c r="A2249" t="inlineStr">
         <is>
-          <t>CL72RSPGJP</t>
+          <t>CL72RSPGGP</t>
         </is>
       </c>
       <c r="B2249" t="n">
@@ -22812,7 +22920,7 @@
     <row r="2250">
       <c r="A2250" t="inlineStr">
         <is>
-          <t>CL72RSPGLP</t>
+          <t>CL72RSPGJP</t>
         </is>
       </c>
       <c r="B2250" t="n">
@@ -22822,37 +22930,37 @@
     <row r="2251">
       <c r="A2251" t="inlineStr">
         <is>
-          <t>CNR900</t>
+          <t>CL72RSPGLP</t>
         </is>
       </c>
       <c r="B2251" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2252">
       <c r="A2252" t="inlineStr">
         <is>
-          <t>CSA15</t>
+          <t>CNR900</t>
         </is>
       </c>
       <c r="B2252" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2253">
       <c r="A2253" t="inlineStr">
         <is>
-          <t>CSA25</t>
+          <t>CSA15</t>
         </is>
       </c>
       <c r="B2253" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2254">
       <c r="A2254" t="inlineStr">
         <is>
-          <t>DH7</t>
+          <t>CSA25</t>
         </is>
       </c>
       <c r="B2254" t="n">
@@ -22862,27 +22970,27 @@
     <row r="2255">
       <c r="A2255" t="inlineStr">
         <is>
-          <t>DKP137MRK</t>
+          <t>DH7</t>
         </is>
       </c>
       <c r="B2255" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2256">
       <c r="A2256" t="inlineStr">
         <is>
-          <t>DKP146MRK</t>
+          <t>DKP137MRK</t>
         </is>
       </c>
       <c r="B2256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2257">
       <c r="A2257" t="inlineStr">
         <is>
-          <t>DMP1255MVM</t>
+          <t>DKP146MRK</t>
         </is>
       </c>
       <c r="B2257" t="n">
@@ -22892,37 +23000,37 @@
     <row r="2258">
       <c r="A2258" t="inlineStr">
         <is>
-          <t>DS30</t>
+          <t>DMP1255MVM</t>
         </is>
       </c>
       <c r="B2258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2259">
       <c r="A2259" t="inlineStr">
         <is>
-          <t>DST1055M</t>
+          <t>DS30</t>
         </is>
       </c>
       <c r="B2259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2260">
       <c r="A2260" t="inlineStr">
         <is>
-          <t>DST1465</t>
+          <t>DST1055M</t>
         </is>
       </c>
       <c r="B2260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2261">
       <c r="A2261" t="inlineStr">
         <is>
-          <t>FB22BMFS</t>
+          <t>DST1465</t>
         </is>
       </c>
       <c r="B2261" t="n">
@@ -22932,7 +23040,7 @@
     <row r="2262">
       <c r="A2262" t="inlineStr">
         <is>
-          <t>HB5W</t>
+          <t>FB22BMFS</t>
         </is>
       </c>
       <c r="B2262" t="n">
@@ -22942,7 +23050,7 @@
     <row r="2263">
       <c r="A2263" t="inlineStr">
         <is>
-          <t>HC103BW</t>
+          <t>HB5W</t>
         </is>
       </c>
       <c r="B2263" t="n">
@@ -22952,14 +23060,17 @@
     <row r="2264">
       <c r="A2264" t="inlineStr">
         <is>
-          <t>HC22W</t>
-        </is>
+          <t>HC103BW</t>
+        </is>
+      </c>
+      <c r="B2264" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2265">
       <c r="A2265" t="inlineStr">
         <is>
-          <t>HC23BW</t>
+          <t>HC22W</t>
         </is>
       </c>
       <c r="B2265" t="n">
@@ -22969,67 +23080,67 @@
     <row r="2266">
       <c r="A2266" t="inlineStr">
         <is>
-          <t>HC32S</t>
+          <t>HC23BW</t>
         </is>
       </c>
       <c r="B2266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2267">
       <c r="A2267" t="inlineStr">
         <is>
-          <t>HC32W</t>
+          <t>HC32S</t>
         </is>
       </c>
       <c r="B2267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2268">
       <c r="A2268" t="inlineStr">
         <is>
-          <t>HC33BW</t>
+          <t>HC32W</t>
         </is>
       </c>
       <c r="B2268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2269">
       <c r="A2269" t="inlineStr">
         <is>
-          <t>HC42WN</t>
+          <t>HC33BW</t>
         </is>
       </c>
       <c r="B2269" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2270">
       <c r="A2270" t="inlineStr">
         <is>
-          <t>HC43BWN</t>
+          <t>HC42WN</t>
         </is>
       </c>
       <c r="B2270" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2271">
       <c r="A2271" t="inlineStr">
         <is>
-          <t>HC43BWNX2</t>
+          <t>HC43BWN</t>
         </is>
       </c>
       <c r="B2271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2272">
       <c r="A2272" t="inlineStr">
         <is>
-          <t>HC4FB</t>
+          <t>HC43BWNX2</t>
         </is>
       </c>
       <c r="B2272" t="n">
@@ -23039,77 +23150,77 @@
     <row r="2273">
       <c r="A2273" t="inlineStr">
         <is>
-          <t>HC63BW</t>
+          <t>HC4FB</t>
         </is>
       </c>
       <c r="B2273" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2274">
       <c r="A2274" t="inlineStr">
         <is>
-          <t>HC72WN</t>
+          <t>HC63BW</t>
         </is>
       </c>
       <c r="B2274" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2275">
       <c r="A2275" t="inlineStr">
         <is>
-          <t>HC73BWN</t>
+          <t>HC72WN</t>
         </is>
       </c>
       <c r="B2275" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2276">
       <c r="A2276" t="inlineStr">
         <is>
-          <t>HC74BWN</t>
+          <t>HC73BWN</t>
         </is>
       </c>
       <c r="B2276" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2277">
       <c r="A2277" t="inlineStr">
         <is>
-          <t>HC83BW</t>
+          <t>HC74BWN</t>
         </is>
       </c>
       <c r="B2277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2278">
       <c r="A2278" t="inlineStr">
         <is>
-          <t>HC83BWX2</t>
+          <t>HC83BW</t>
         </is>
       </c>
       <c r="B2278" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2279">
       <c r="A2279" t="inlineStr">
         <is>
-          <t>HH205</t>
+          <t>HC83BWX2</t>
         </is>
       </c>
       <c r="B2279" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2280">
       <c r="A2280" t="inlineStr">
         <is>
-          <t>HH205S</t>
+          <t>HH205</t>
         </is>
       </c>
       <c r="B2280" t="n">
@@ -23119,7 +23230,7 @@
     <row r="2281">
       <c r="A2281" t="inlineStr">
         <is>
-          <t>HH315D</t>
+          <t>HH205S</t>
         </is>
       </c>
       <c r="B2281" t="n">
@@ -23129,7 +23240,7 @@
     <row r="2282">
       <c r="A2282" t="inlineStr">
         <is>
-          <t>HH45WN</t>
+          <t>HH315D</t>
         </is>
       </c>
       <c r="B2282" t="n">
@@ -23139,7 +23250,7 @@
     <row r="2283">
       <c r="A2283" t="inlineStr">
         <is>
-          <t>HH605</t>
+          <t>HH45WN</t>
         </is>
       </c>
       <c r="B2283" t="n">
@@ -23149,7 +23260,7 @@
     <row r="2284">
       <c r="A2284" t="inlineStr">
         <is>
-          <t>HH75WN</t>
+          <t>HH605</t>
         </is>
       </c>
       <c r="B2284" t="n">
@@ -23159,47 +23270,47 @@
     <row r="2285">
       <c r="A2285" t="inlineStr">
         <is>
-          <t>HH805D</t>
+          <t>HH75WN</t>
         </is>
       </c>
       <c r="B2285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2286">
       <c r="A2286" t="inlineStr">
         <is>
-          <t>HH905D</t>
+          <t>HH805D</t>
         </is>
       </c>
       <c r="B2286" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2287">
       <c r="A2287" t="inlineStr">
         <is>
-          <t>HH905N</t>
+          <t>HH905D</t>
         </is>
       </c>
       <c r="B2287" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2288">
       <c r="A2288" t="inlineStr">
         <is>
-          <t>HH915D</t>
+          <t>HH905N</t>
         </is>
       </c>
       <c r="B2288" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2289">
       <c r="A2289" t="inlineStr">
         <is>
-          <t>HHDS1</t>
+          <t>HH915D</t>
         </is>
       </c>
       <c r="B2289" t="n">
@@ -23209,37 +23320,37 @@
     <row r="2290">
       <c r="A2290" t="inlineStr">
         <is>
-          <t>HP200P</t>
+          <t>HHDS1</t>
         </is>
       </c>
       <c r="B2290" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2291">
       <c r="A2291" t="inlineStr">
         <is>
-          <t>HP200PTW</t>
+          <t>HP200P</t>
         </is>
       </c>
       <c r="B2291" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2292">
       <c r="A2292" t="inlineStr">
         <is>
-          <t>HP30</t>
+          <t>HP200PTW</t>
         </is>
       </c>
       <c r="B2292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2293">
       <c r="A2293" t="inlineStr">
         <is>
-          <t>HP300B</t>
+          <t>HP30</t>
         </is>
       </c>
       <c r="B2293" t="n">
@@ -23249,17 +23360,17 @@
     <row r="2294">
       <c r="A2294" t="inlineStr">
         <is>
-          <t>HP300TWB</t>
+          <t>HP300B</t>
         </is>
       </c>
       <c r="B2294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2295">
       <c r="A2295" t="inlineStr">
         <is>
-          <t>HP30TW</t>
+          <t>HP300TWB</t>
         </is>
       </c>
       <c r="B2295" t="n">
@@ -23269,7 +23380,7 @@
     <row r="2296">
       <c r="A2296" t="inlineStr">
         <is>
-          <t>HP310L</t>
+          <t>HP30TW</t>
         </is>
       </c>
       <c r="B2296" t="n">
@@ -23279,7 +23390,7 @@
     <row r="2297">
       <c r="A2297" t="inlineStr">
         <is>
-          <t>HP310LW</t>
+          <t>HP310L</t>
         </is>
       </c>
       <c r="B2297" t="n">
@@ -23289,27 +23400,27 @@
     <row r="2298">
       <c r="A2298" t="inlineStr">
         <is>
-          <t>HP50</t>
+          <t>HP310LW</t>
         </is>
       </c>
       <c r="B2298" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2299">
       <c r="A2299" t="inlineStr">
         <is>
-          <t>HP600D</t>
+          <t>HP50</t>
         </is>
       </c>
       <c r="B2299" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2300">
       <c r="A2300" t="inlineStr">
         <is>
-          <t>HP600DTW</t>
+          <t>HP600D</t>
         </is>
       </c>
       <c r="B2300" t="n">
@@ -23319,7 +23430,7 @@
     <row r="2301">
       <c r="A2301" t="inlineStr">
         <is>
-          <t>HP600DTWB</t>
+          <t>HP600DTW</t>
         </is>
       </c>
       <c r="B2301" t="n">
@@ -23329,17 +23440,17 @@
     <row r="2302">
       <c r="A2302" t="inlineStr">
         <is>
-          <t>HP900 7H</t>
+          <t>HP600DTWB</t>
         </is>
       </c>
       <c r="B2302" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2303">
       <c r="A2303" t="inlineStr">
         <is>
-          <t>HP900 7R</t>
+          <t>HP900 7H</t>
         </is>
       </c>
       <c r="B2303" t="n">
@@ -23349,17 +23460,17 @@
     <row r="2304">
       <c r="A2304" t="inlineStr">
         <is>
-          <t>HP900FSN</t>
+          <t>HP900 7R</t>
         </is>
       </c>
       <c r="B2304" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2305">
       <c r="A2305" t="inlineStr">
         <is>
-          <t>HP900FSWN</t>
+          <t>HP900FSN</t>
         </is>
       </c>
       <c r="B2305" t="n">
@@ -23369,7 +23480,7 @@
     <row r="2306">
       <c r="A2306" t="inlineStr">
         <is>
-          <t>HP900PMCS</t>
+          <t>HP900FSWN</t>
         </is>
       </c>
       <c r="B2306" t="n">
@@ -23379,37 +23490,37 @@
     <row r="2307">
       <c r="A2307" t="inlineStr">
         <is>
-          <t>HP900PMPR</t>
+          <t>HP900PMCS</t>
         </is>
       </c>
       <c r="B2307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2308">
       <c r="A2308" t="inlineStr">
         <is>
-          <t>HP900PN</t>
+          <t>HP900PMPR</t>
         </is>
       </c>
       <c r="B2308" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2309">
       <c r="A2309" t="inlineStr">
         <is>
-          <t>HP900PSN</t>
+          <t>HP900PN</t>
         </is>
       </c>
       <c r="B2309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2310">
       <c r="A2310" t="inlineStr">
         <is>
-          <t>HP900PSWN</t>
+          <t>HP900PSN</t>
         </is>
       </c>
       <c r="B2310" t="n">
@@ -23419,17 +23530,17 @@
     <row r="2311">
       <c r="A2311" t="inlineStr">
         <is>
-          <t>HP900PWMCS</t>
+          <t>HP900PSWN</t>
         </is>
       </c>
       <c r="B2311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2312">
       <c r="A2312" t="inlineStr">
         <is>
-          <t>HP900PWMPR</t>
+          <t>HP900PWMCS</t>
         </is>
       </c>
       <c r="B2312" t="n">
@@ -23439,17 +23550,17 @@
     <row r="2313">
       <c r="A2313" t="inlineStr">
         <is>
-          <t>HP900PWN</t>
+          <t>HP900PWMPR</t>
         </is>
       </c>
       <c r="B2313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2314">
       <c r="A2314" t="inlineStr">
         <is>
-          <t>HP900PWNMR</t>
+          <t>HP900PWN</t>
         </is>
       </c>
       <c r="B2314" t="n">
@@ -23459,7 +23570,7 @@
     <row r="2315">
       <c r="A2315" t="inlineStr">
         <is>
-          <t>HP900RMCS</t>
+          <t>HP900PWNMR</t>
         </is>
       </c>
       <c r="B2315" t="n">
@@ -23469,7 +23580,7 @@
     <row r="2316">
       <c r="A2316" t="inlineStr">
         <is>
-          <t>HP900RMPR</t>
+          <t>HP900RMCS</t>
         </is>
       </c>
       <c r="B2316" t="n">
@@ -23479,17 +23590,17 @@
     <row r="2317">
       <c r="A2317" t="inlineStr">
         <is>
-          <t>HP900RN</t>
+          <t>HP900RMPR</t>
         </is>
       </c>
       <c r="B2317" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2318">
       <c r="A2318" t="inlineStr">
         <is>
-          <t>HP900RSN</t>
+          <t>HP900RN</t>
         </is>
       </c>
       <c r="B2318" t="n">
@@ -23499,7 +23610,7 @@
     <row r="2319">
       <c r="A2319" t="inlineStr">
         <is>
-          <t>HP900RSWN</t>
+          <t>HP900RSN</t>
         </is>
       </c>
       <c r="B2319" t="n">
@@ -23509,17 +23620,17 @@
     <row r="2320">
       <c r="A2320" t="inlineStr">
         <is>
-          <t>HP900RWMCS</t>
+          <t>HP900RSWN</t>
         </is>
       </c>
       <c r="B2320" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2321">
       <c r="A2321" t="inlineStr">
         <is>
-          <t>HP900RWMPR</t>
+          <t>HP900RWMCS</t>
         </is>
       </c>
       <c r="B2321" t="n">
@@ -23529,17 +23640,17 @@
     <row r="2322">
       <c r="A2322" t="inlineStr">
         <is>
-          <t>HP900RWN</t>
+          <t>HP900RWMPR</t>
         </is>
       </c>
       <c r="B2322" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2323">
       <c r="A2323" t="inlineStr">
         <is>
-          <t>HP909</t>
+          <t>HP900RWN</t>
         </is>
       </c>
       <c r="B2323" t="n">
@@ -23549,17 +23660,17 @@
     <row r="2324">
       <c r="A2324" t="inlineStr">
         <is>
-          <t>HP910 7S</t>
+          <t>HP909</t>
         </is>
       </c>
       <c r="B2324" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2325">
       <c r="A2325" t="inlineStr">
         <is>
-          <t>HP910LN</t>
+          <t>HP910 7S</t>
         </is>
       </c>
       <c r="B2325" t="n">
@@ -23569,27 +23680,27 @@
     <row r="2326">
       <c r="A2326" t="inlineStr">
         <is>
-          <t>HP910LS</t>
+          <t>HP910LN</t>
         </is>
       </c>
       <c r="B2326" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2327">
       <c r="A2327" t="inlineStr">
         <is>
-          <t>HP910LSW</t>
+          <t>HP910LS</t>
         </is>
       </c>
       <c r="B2327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2328">
       <c r="A2328" t="inlineStr">
         <is>
-          <t>HP910LWCB</t>
+          <t>HP910LSW</t>
         </is>
       </c>
       <c r="B2328" t="n">
@@ -23599,47 +23710,47 @@
     <row r="2329">
       <c r="A2329" t="inlineStr">
         <is>
-          <t>HP910LWN</t>
+          <t>HP910LWCB</t>
         </is>
       </c>
       <c r="B2329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2330">
       <c r="A2330" t="inlineStr">
         <is>
-          <t>HP910LWNMR</t>
+          <t>HP910LWN</t>
         </is>
       </c>
       <c r="B2330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2331">
       <c r="A2331" t="inlineStr">
         <is>
-          <t>HPDS1</t>
+          <t>HP910LWNMR</t>
         </is>
       </c>
       <c r="B2331" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2332">
       <c r="A2332" t="inlineStr">
         <is>
-          <t>HPDS1TW</t>
+          <t>HPDS1</t>
         </is>
       </c>
       <c r="B2332" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2333">
       <c r="A2333" t="inlineStr">
         <is>
-          <t>HS100W</t>
+          <t>HPDS1TW</t>
         </is>
       </c>
       <c r="B2333" t="n">
@@ -23649,17 +23760,17 @@
     <row r="2334">
       <c r="A2334" t="inlineStr">
         <is>
-          <t>HS40WN</t>
+          <t>HS100W</t>
         </is>
       </c>
       <c r="B2334" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2335">
       <c r="A2335" t="inlineStr">
         <is>
-          <t>HS70PWN</t>
+          <t>HS40WN</t>
         </is>
       </c>
       <c r="B2335" t="n">
@@ -23669,67 +23780,67 @@
     <row r="2336">
       <c r="A2336" t="inlineStr">
         <is>
-          <t>HS70WN</t>
+          <t>HS70PWN</t>
         </is>
       </c>
       <c r="B2336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2337">
       <c r="A2337" t="inlineStr">
         <is>
-          <t>HS800W</t>
+          <t>HS70WN</t>
         </is>
       </c>
       <c r="B2337" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2338">
       <c r="A2338" t="inlineStr">
         <is>
-          <t>HS80LOW</t>
+          <t>HS800W</t>
         </is>
       </c>
       <c r="B2338" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2339">
       <c r="A2339" t="inlineStr">
         <is>
-          <t>HS80PW</t>
+          <t>HS80LOW</t>
         </is>
       </c>
       <c r="B2339" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2340">
       <c r="A2340" t="inlineStr">
         <is>
-          <t>HS80W</t>
+          <t>HS80PW</t>
         </is>
       </c>
       <c r="B2340" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2341">
       <c r="A2341" t="inlineStr">
         <is>
-          <t>HT130</t>
+          <t>HS80W</t>
         </is>
       </c>
       <c r="B2341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2342">
       <c r="A2342" t="inlineStr">
         <is>
-          <t>HT230</t>
+          <t>HT130</t>
         </is>
       </c>
       <c r="B2342" t="n">
@@ -23739,7 +23850,7 @@
     <row r="2343">
       <c r="A2343" t="inlineStr">
         <is>
-          <t>HT230LOW</t>
+          <t>HT230</t>
         </is>
       </c>
       <c r="B2343" t="n">
@@ -23749,7 +23860,7 @@
     <row r="2344">
       <c r="A2344" t="inlineStr">
         <is>
-          <t>HT30</t>
+          <t>HT230LOW</t>
         </is>
       </c>
       <c r="B2344" t="n">
@@ -23759,7 +23870,7 @@
     <row r="2345">
       <c r="A2345" t="inlineStr">
         <is>
-          <t>HT330</t>
+          <t>HT30</t>
         </is>
       </c>
       <c r="B2345" t="n">
@@ -23769,7 +23880,7 @@
     <row r="2346">
       <c r="A2346" t="inlineStr">
         <is>
-          <t>HT430B</t>
+          <t>HT330</t>
         </is>
       </c>
       <c r="B2346" t="n">
@@ -23779,7 +23890,7 @@
     <row r="2347">
       <c r="A2347" t="inlineStr">
         <is>
-          <t>HT430BC</t>
+          <t>HT430B</t>
         </is>
       </c>
       <c r="B2347" t="n">
@@ -23789,67 +23900,67 @@
     <row r="2348">
       <c r="A2348" t="inlineStr">
         <is>
-          <t>HT530B</t>
+          <t>HT430BC</t>
         </is>
       </c>
       <c r="B2348" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2349">
       <c r="A2349" t="inlineStr">
         <is>
-          <t>HT530BC</t>
+          <t>HT530B</t>
         </is>
       </c>
       <c r="B2349" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2350">
       <c r="A2350" t="inlineStr">
         <is>
-          <t>HT530BCN</t>
+          <t>HT530BC</t>
         </is>
       </c>
       <c r="B2350" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2351">
       <c r="A2351" t="inlineStr">
         <is>
-          <t>HT550BCN</t>
+          <t>HT530BCN</t>
         </is>
       </c>
       <c r="B2351" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2352">
       <c r="A2352" t="inlineStr">
         <is>
-          <t>HT650C</t>
+          <t>HT550BCN</t>
         </is>
       </c>
       <c r="B2352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2353">
       <c r="A2353" t="inlineStr">
         <is>
-          <t>HT65WN</t>
+          <t>HT650C</t>
         </is>
       </c>
       <c r="B2353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2354">
       <c r="A2354" t="inlineStr">
         <is>
-          <t>HT730B</t>
+          <t>HT65WN</t>
         </is>
       </c>
       <c r="B2354" t="n">
@@ -23859,17 +23970,17 @@
     <row r="2355">
       <c r="A2355" t="inlineStr">
         <is>
-          <t>HT741B</t>
+          <t>HT730B</t>
         </is>
       </c>
       <c r="B2355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2356">
       <c r="A2356" t="inlineStr">
         <is>
-          <t>HT750BC</t>
+          <t>HT741B</t>
         </is>
       </c>
       <c r="B2356" t="n">
@@ -23879,7 +23990,7 @@
     <row r="2357">
       <c r="A2357" t="inlineStr">
         <is>
-          <t>HT750C</t>
+          <t>HT750BC</t>
         </is>
       </c>
       <c r="B2357" t="n">
@@ -23889,7 +24000,7 @@
     <row r="2358">
       <c r="A2358" t="inlineStr">
         <is>
-          <t>HT75WN</t>
+          <t>HT750C</t>
         </is>
       </c>
       <c r="B2358" t="n">
@@ -23899,14 +24010,17 @@
     <row r="2359">
       <c r="A2359" t="inlineStr">
         <is>
-          <t>HT830B</t>
-        </is>
+          <t>HT75WN</t>
+        </is>
+      </c>
+      <c r="B2359" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2360">
       <c r="A2360" t="inlineStr">
         <is>
-          <t>HT850BC</t>
+          <t>HT830B</t>
         </is>
       </c>
       <c r="B2360" t="n">
@@ -23916,14 +24030,17 @@
     <row r="2361">
       <c r="A2361" t="inlineStr">
         <is>
-          <t>HTC707WN</t>
-        </is>
+          <t>HT850BC</t>
+        </is>
+      </c>
+      <c r="B2361" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="2362">
       <c r="A2362" t="inlineStr">
         <is>
-          <t>HTC807W</t>
+          <t>HTC707WN</t>
         </is>
       </c>
       <c r="B2362" t="n">
@@ -23933,14 +24050,17 @@
     <row r="2363">
       <c r="A2363" t="inlineStr">
         <is>
-          <t>HTS88W</t>
-        </is>
+          <t>HTC807W</t>
+        </is>
+      </c>
+      <c r="B2363" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2364">
       <c r="A2364" t="inlineStr">
         <is>
-          <t>HTW839W</t>
+          <t>HTS88W</t>
         </is>
       </c>
       <c r="B2364" t="n">
@@ -23950,7 +24070,7 @@
     <row r="2365">
       <c r="A2365" t="inlineStr">
         <is>
-          <t>LAL1455</t>
+          <t>HTW839W</t>
         </is>
       </c>
       <c r="B2365" t="n">
@@ -23960,74 +24080,77 @@
     <row r="2366">
       <c r="A2366" t="inlineStr">
         <is>
-          <t>LBH1410LTM</t>
+          <t>LAL1455</t>
         </is>
       </c>
       <c r="B2366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2367">
       <c r="A2367" t="inlineStr">
         <is>
-          <t>LBR144</t>
+          <t>LBH1410LTM</t>
         </is>
       </c>
       <c r="B2367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2368">
       <c r="A2368" t="inlineStr">
         <is>
-          <t>LBR1465</t>
+          <t>LBR144</t>
         </is>
       </c>
       <c r="B2368" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2369">
       <c r="A2369" t="inlineStr">
         <is>
-          <t>LBU127SBG</t>
+          <t>LBR1465</t>
         </is>
       </c>
       <c r="B2369" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2370">
       <c r="A2370" t="inlineStr">
         <is>
-          <t>LGB146NQB</t>
+          <t>LBU127SBG</t>
         </is>
       </c>
       <c r="B2370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2371">
       <c r="A2371" t="inlineStr">
         <is>
-          <t>LGM137STA</t>
+          <t>LGB146NQB</t>
         </is>
       </c>
       <c r="B2371" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2372">
       <c r="A2372" t="inlineStr">
         <is>
-          <t>LGM146KMB</t>
-        </is>
+          <t>LGM137STA</t>
+        </is>
+      </c>
+      <c r="B2372" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="2373">
       <c r="A2373" t="inlineStr">
         <is>
-          <t>LJK28H4AQB</t>
+          <t>LGM146KMB</t>
         </is>
       </c>
       <c r="B2373" t="n">
@@ -24037,7 +24160,7 @@
     <row r="2374">
       <c r="A2374" t="inlineStr">
         <is>
-          <t>LJK28H4CCM</t>
+          <t>LJK28H4AQB</t>
         </is>
       </c>
       <c r="B2374" t="n">
@@ -24047,7 +24170,7 @@
     <row r="2375">
       <c r="A2375" t="inlineStr">
         <is>
-          <t>LJK44H4AQB</t>
+          <t>LJK28H4CCM</t>
         </is>
       </c>
       <c r="B2375" t="n">
@@ -24057,7 +24180,7 @@
     <row r="2376">
       <c r="A2376" t="inlineStr">
         <is>
-          <t>LJK44H4CPM</t>
+          <t>LJK44H4AQB</t>
         </is>
       </c>
       <c r="B2376" t="n">
@@ -24067,7 +24190,7 @@
     <row r="2377">
       <c r="A2377" t="inlineStr">
         <is>
-          <t>LJK48H4AQB</t>
+          <t>LJK44H4CPM</t>
         </is>
       </c>
       <c r="B2377" t="n">
@@ -24077,7 +24200,7 @@
     <row r="2378">
       <c r="A2378" t="inlineStr">
         <is>
-          <t>LJK48H4CCM</t>
+          <t>LJK48H4AQB</t>
         </is>
       </c>
       <c r="B2378" t="n">
@@ -24087,7 +24210,7 @@
     <row r="2379">
       <c r="A2379" t="inlineStr">
         <is>
-          <t>LJK48H4CMW</t>
+          <t>LJK48H4CCM</t>
         </is>
       </c>
       <c r="B2379" t="n">
@@ -24097,7 +24220,7 @@
     <row r="2380">
       <c r="A2380" t="inlineStr">
         <is>
-          <t>LJL48H4SBE</t>
+          <t>LJK48H4CMW</t>
         </is>
       </c>
       <c r="B2380" t="n">
@@ -24107,7 +24230,7 @@
     <row r="2381">
       <c r="A2381" t="inlineStr">
         <is>
-          <t>LJL48H4SBO</t>
+          <t>LJL48H4SBE</t>
         </is>
       </c>
       <c r="B2381" t="n">
@@ -24117,7 +24240,7 @@
     <row r="2382">
       <c r="A2382" t="inlineStr">
         <is>
-          <t>LKP1465KPB</t>
+          <t>LJL48H4SBO</t>
         </is>
       </c>
       <c r="B2382" t="n">
@@ -24127,7 +24250,7 @@
     <row r="2383">
       <c r="A2383" t="inlineStr">
         <is>
-          <t>LKP42HTSGK</t>
+          <t>LKP1465KPB</t>
         </is>
       </c>
       <c r="B2383" t="n">
@@ -24137,17 +24260,17 @@
     <row r="2384">
       <c r="A2384" t="inlineStr">
         <is>
-          <t>LMB1465MMB</t>
+          <t>LKP42HTSGK</t>
         </is>
       </c>
       <c r="B2384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2385">
       <c r="A2385" t="inlineStr">
         <is>
-          <t>LMP1455MP</t>
+          <t>LMB1465MMB</t>
         </is>
       </c>
       <c r="B2385" t="n">
@@ -24157,34 +24280,37 @@
     <row r="2386">
       <c r="A2386" t="inlineStr">
         <is>
-          <t>LMP1455SMP</t>
-        </is>
+          <t>LMP1455MP</t>
+        </is>
+      </c>
+      <c r="B2386" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2387">
       <c r="A2387" t="inlineStr">
         <is>
-          <t>LMP1465FSN</t>
+          <t>LMP1455SMP</t>
         </is>
       </c>
       <c r="B2387" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2388">
       <c r="A2388" t="inlineStr">
         <is>
-          <t>LMP1465SEN</t>
+          <t>LMP1465FSN</t>
         </is>
       </c>
       <c r="B2388" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2389">
       <c r="A2389" t="inlineStr">
         <is>
-          <t>LSP146WSS</t>
+          <t>LMP1465SEN</t>
         </is>
       </c>
       <c r="B2389" t="n">
@@ -24194,17 +24320,17 @@
     <row r="2390">
       <c r="A2390" t="inlineStr">
         <is>
-          <t>LSP30CSTWS</t>
+          <t>LSP146WSS</t>
         </is>
       </c>
       <c r="B2390" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2391">
       <c r="A2391" t="inlineStr">
         <is>
-          <t>LSS1465</t>
+          <t>LSP30CSTWS</t>
         </is>
       </c>
       <c r="B2391" t="n">
@@ -24214,7 +24340,7 @@
     <row r="2392">
       <c r="A2392" t="inlineStr">
         <is>
-          <t>LST148</t>
+          <t>LSS1465</t>
         </is>
       </c>
       <c r="B2392" t="n">
@@ -24224,7 +24350,7 @@
     <row r="2393">
       <c r="A2393" t="inlineStr">
         <is>
-          <t>MA32RZSCHS</t>
+          <t>LST148</t>
         </is>
       </c>
       <c r="B2393" t="n">
@@ -24234,7 +24360,7 @@
     <row r="2394">
       <c r="A2394" t="inlineStr">
         <is>
-          <t>MA34CZSCHS</t>
+          <t>MA32RZSCHS</t>
         </is>
       </c>
       <c r="B2394" t="n">
@@ -24244,7 +24370,7 @@
     <row r="2395">
       <c r="A2395" t="inlineStr">
         <is>
-          <t>MA34CZSPBK</t>
+          <t>MA34CZSCHS</t>
         </is>
       </c>
       <c r="B2395" t="n">
@@ -24254,21 +24380,27 @@
     <row r="2396">
       <c r="A2396" t="inlineStr">
         <is>
-          <t>MAB1814M</t>
-        </is>
+          <t>MA34CZSPBK</t>
+        </is>
+      </c>
+      <c r="B2396" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2397">
       <c r="A2397" t="inlineStr">
         <is>
-          <t>MAB2016M</t>
-        </is>
+          <t>MAB1814M</t>
+        </is>
+      </c>
+      <c r="B2397" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2398">
       <c r="A2398" t="inlineStr">
         <is>
-          <t>MAB2218FBK</t>
+          <t>MAB2016M</t>
         </is>
       </c>
       <c r="B2398" t="n">
@@ -24278,14 +24410,17 @@
     <row r="2399">
       <c r="A2399" t="inlineStr">
         <is>
-          <t>MAB2218M</t>
-        </is>
+          <t>MAB2218FBK</t>
+        </is>
+      </c>
+      <c r="B2399" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2400">
       <c r="A2400" t="inlineStr">
         <is>
-          <t>MAB2218PBK</t>
+          <t>MAB2218M</t>
         </is>
       </c>
       <c r="B2400" t="n">
@@ -24295,14 +24430,17 @@
     <row r="2401">
       <c r="A2401" t="inlineStr">
         <is>
-          <t>MAF1412</t>
-        </is>
+          <t>MAB2218PBK</t>
+        </is>
+      </c>
+      <c r="B2401" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2402">
       <c r="A2402" t="inlineStr">
         <is>
-          <t>MAF1414FBK</t>
+          <t>MAF1412</t>
         </is>
       </c>
       <c r="B2402" t="n">
@@ -24312,7 +24450,7 @@
     <row r="2403">
       <c r="A2403" t="inlineStr">
         <is>
-          <t>MAF1414PBK</t>
+          <t>MAF1414FBK</t>
         </is>
       </c>
       <c r="B2403" t="n">
@@ -24322,14 +24460,17 @@
     <row r="2404">
       <c r="A2404" t="inlineStr">
         <is>
-          <t>MAF1616</t>
-        </is>
+          <t>MAF1414PBK</t>
+        </is>
+      </c>
+      <c r="B2404" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2405">
       <c r="A2405" t="inlineStr">
         <is>
-          <t>MAF1616FBK</t>
+          <t>MAF1616</t>
         </is>
       </c>
       <c r="B2405" t="n">
@@ -24339,7 +24480,7 @@
     <row r="2406">
       <c r="A2406" t="inlineStr">
         <is>
-          <t>MAF1616PBK</t>
+          <t>MAF1616FBK</t>
         </is>
       </c>
       <c r="B2406" t="n">
@@ -24349,14 +24490,17 @@
     <row r="2407">
       <c r="A2407" t="inlineStr">
         <is>
-          <t>MAF1816</t>
-        </is>
+          <t>MAF1616PBK</t>
+        </is>
+      </c>
+      <c r="B2407" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2408">
       <c r="A2408" t="inlineStr">
         <is>
-          <t>MAF1816FBK</t>
+          <t>MAF1816</t>
         </is>
       </c>
       <c r="B2408" t="n">
@@ -24366,7 +24510,7 @@
     <row r="2409">
       <c r="A2409" t="inlineStr">
         <is>
-          <t>MAF1816PBK</t>
+          <t>MAF1816FBK</t>
         </is>
       </c>
       <c r="B2409" t="n">
@@ -24376,7 +24520,7 @@
     <row r="2410">
       <c r="A2410" t="inlineStr">
         <is>
-          <t>MAS1455</t>
+          <t>MAF1816PBK</t>
         </is>
       </c>
       <c r="B2410" t="n">
@@ -24386,7 +24530,7 @@
     <row r="2411">
       <c r="A2411" t="inlineStr">
         <is>
-          <t>MAS1455ATM</t>
+          <t>MAS1455</t>
         </is>
       </c>
       <c r="B2411" t="n">
@@ -24396,7 +24540,7 @@
     <row r="2412">
       <c r="A2412" t="inlineStr">
         <is>
-          <t>MAT0806BPW</t>
+          <t>MAS1455ATM</t>
         </is>
       </c>
       <c r="B2412" t="n">
@@ -24406,7 +24550,7 @@
     <row r="2413">
       <c r="A2413" t="inlineStr">
         <is>
-          <t>MAT0806FBK</t>
+          <t>MAT0806BPW</t>
         </is>
       </c>
       <c r="B2413" t="n">
@@ -24416,14 +24560,17 @@
     <row r="2414">
       <c r="A2414" t="inlineStr">
         <is>
-          <t>MAT0807</t>
-        </is>
+          <t>MAT0806FBK</t>
+        </is>
+      </c>
+      <c r="B2414" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2415">
       <c r="A2415" t="inlineStr">
         <is>
-          <t>MAT1007BPW</t>
+          <t>MAT0807</t>
         </is>
       </c>
       <c r="B2415" t="n">
@@ -24433,7 +24580,7 @@
     <row r="2416">
       <c r="A2416" t="inlineStr">
         <is>
-          <t>MAT1007FBK</t>
+          <t>MAT1007BPW</t>
         </is>
       </c>
       <c r="B2416" t="n">
@@ -24443,24 +24590,27 @@
     <row r="2417">
       <c r="A2417" t="inlineStr">
         <is>
-          <t>MAT1008</t>
+          <t>MAT1007FBK</t>
         </is>
       </c>
       <c r="B2417" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2418">
       <c r="A2418" t="inlineStr">
         <is>
-          <t>MAT1008BPB</t>
-        </is>
+          <t>MAT1008</t>
+        </is>
+      </c>
+      <c r="B2418" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2419">
       <c r="A2419" t="inlineStr">
         <is>
-          <t>MAT1008PBK</t>
+          <t>MAT1008BPB</t>
         </is>
       </c>
       <c r="B2419" t="n">
@@ -24470,7 +24620,7 @@
     <row r="2420">
       <c r="A2420" t="inlineStr">
         <is>
-          <t>MAT1208FBK</t>
+          <t>MAT1008PBK</t>
         </is>
       </c>
       <c r="B2420" t="n">
@@ -24480,14 +24630,17 @@
     <row r="2421">
       <c r="A2421" t="inlineStr">
         <is>
-          <t>MAT1209</t>
-        </is>
+          <t>MAT1208FBK</t>
+        </is>
+      </c>
+      <c r="B2421" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2422">
       <c r="A2422" t="inlineStr">
         <is>
-          <t>MAT1210BPB</t>
+          <t>MAT1209</t>
         </is>
       </c>
       <c r="B2422" t="n">
@@ -24497,7 +24650,7 @@
     <row r="2423">
       <c r="A2423" t="inlineStr">
         <is>
-          <t>MAT1309FBK</t>
+          <t>MAT1210BPB</t>
         </is>
       </c>
       <c r="B2423" t="n">
@@ -24507,14 +24660,17 @@
     <row r="2424">
       <c r="A2424" t="inlineStr">
         <is>
-          <t>MAT1410</t>
-        </is>
+          <t>MAT1309FBK</t>
+        </is>
+      </c>
+      <c r="B2424" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2425">
       <c r="A2425" t="inlineStr">
         <is>
-          <t>MBS42SMSL</t>
+          <t>MAT1410</t>
         </is>
       </c>
       <c r="B2425" t="n">
@@ -24524,7 +24680,7 @@
     <row r="2426">
       <c r="A2426" t="inlineStr">
         <is>
-          <t>MBS42SSKA</t>
+          <t>MBS42SMSL</t>
         </is>
       </c>
       <c r="B2426" t="n">
@@ -24534,7 +24690,7 @@
     <row r="2427">
       <c r="A2427" t="inlineStr">
         <is>
-          <t>MBS52RZSDC</t>
+          <t>MBS42SSKA</t>
         </is>
       </c>
       <c r="B2427" t="n">
@@ -24544,7 +24700,7 @@
     <row r="2428">
       <c r="A2428" t="inlineStr">
         <is>
-          <t>MBS52RZSPB</t>
+          <t>MBS52RZSDC</t>
         </is>
       </c>
       <c r="B2428" t="n">
@@ -24554,27 +24710,27 @@
     <row r="2429">
       <c r="A2429" t="inlineStr">
         <is>
-          <t>MC61</t>
+          <t>MBS52RZSPB</t>
         </is>
       </c>
       <c r="B2429" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2430">
       <c r="A2430" t="inlineStr">
         <is>
-          <t>MC62</t>
+          <t>MC61</t>
         </is>
       </c>
       <c r="B2430" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2431">
       <c r="A2431" t="inlineStr">
         <is>
-          <t>MC69</t>
+          <t>MC62</t>
         </is>
       </c>
       <c r="B2431" t="n">
@@ -24584,7 +24740,7 @@
     <row r="2432">
       <c r="A2432" t="inlineStr">
         <is>
-          <t>MCA63EN</t>
+          <t>MC69</t>
         </is>
       </c>
       <c r="B2432" t="n">
@@ -24594,17 +24750,17 @@
     <row r="2433">
       <c r="A2433" t="inlineStr">
         <is>
-          <t>ME32CZSVMF</t>
+          <t>MCA63EN</t>
         </is>
       </c>
       <c r="B2433" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2434">
       <c r="A2434" t="inlineStr">
         <is>
-          <t>ME42TZBTBV</t>
+          <t>ME32CZSVMF</t>
         </is>
       </c>
       <c r="B2434" t="n">
@@ -24614,7 +24770,7 @@
     <row r="2435">
       <c r="A2435" t="inlineStr">
         <is>
-          <t>ME42TZLRWB</t>
+          <t>ME42TZBTBV</t>
         </is>
       </c>
       <c r="B2435" t="n">
@@ -24624,7 +24780,7 @@
     <row r="2436">
       <c r="A2436" t="inlineStr">
         <is>
-          <t>ME42TZSVMF</t>
+          <t>ME42TZLRWB</t>
         </is>
       </c>
       <c r="B2436" t="n">
@@ -24634,7 +24790,7 @@
     <row r="2437">
       <c r="A2437" t="inlineStr">
         <is>
-          <t>ME42TZVGLM</t>
+          <t>ME42TZSVMF</t>
         </is>
       </c>
       <c r="B2437" t="n">
@@ -24644,21 +24800,27 @@
     <row r="2438">
       <c r="A2438" t="inlineStr">
         <is>
-          <t>MHA623</t>
-        </is>
+          <t>ME42TZVGLM</t>
+        </is>
+      </c>
+      <c r="B2438" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="2439">
       <c r="A2439" t="inlineStr">
         <is>
-          <t>MHA823</t>
-        </is>
+          <t>MHA623</t>
+        </is>
+      </c>
+      <c r="B2439" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2440">
       <c r="A2440" t="inlineStr">
         <is>
-          <t>ML52HZBCCW</t>
+          <t>MHA823</t>
         </is>
       </c>
       <c r="B2440" t="n">
@@ -24668,7 +24830,7 @@
     <row r="2441">
       <c r="A2441" t="inlineStr">
         <is>
-          <t>MPH63</t>
+          <t>ML52HZBCCW</t>
         </is>
       </c>
       <c r="B2441" t="n">
@@ -24678,17 +24840,17 @@
     <row r="2442">
       <c r="A2442" t="inlineStr">
         <is>
-          <t>MR42TZBBWO</t>
+          <t>MPH63</t>
         </is>
       </c>
       <c r="B2442" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2443">
       <c r="A2443" t="inlineStr">
         <is>
-          <t>MR42TZSROY</t>
+          <t>MR42TZBBWO</t>
         </is>
       </c>
       <c r="B2443" t="n">
@@ -24698,17 +24860,17 @@
     <row r="2444">
       <c r="A2444" t="inlineStr">
         <is>
-          <t>MR42TZSSLW</t>
+          <t>MR42TZSROY</t>
         </is>
       </c>
       <c r="B2444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2445">
       <c r="A2445" t="inlineStr">
         <is>
-          <t>MR42TZSTQP</t>
+          <t>MR42TZSSLW</t>
         </is>
       </c>
       <c r="B2445" t="n">
@@ -24718,34 +24880,37 @@
     <row r="2446">
       <c r="A2446" t="inlineStr">
         <is>
-          <t>MT1055M</t>
+          <t>MR42TZSTQP</t>
         </is>
       </c>
       <c r="B2446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2447">
       <c r="A2447" t="inlineStr">
         <is>
-          <t>MT1255</t>
-        </is>
+          <t>MT1055M</t>
+        </is>
+      </c>
+      <c r="B2447" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2448">
       <c r="A2448" t="inlineStr">
         <is>
-          <t>MTH1000</t>
+          <t>MT1255</t>
         </is>
       </c>
       <c r="B2448" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2449">
       <c r="A2449" t="inlineStr">
         <is>
-          <t>MTH1000S</t>
+          <t>MTH1000</t>
         </is>
       </c>
       <c r="B2449" t="n">
@@ -24755,27 +24920,27 @@
     <row r="2450">
       <c r="A2450" t="inlineStr">
         <is>
-          <t>MTH900AS</t>
+          <t>MTH1000S</t>
         </is>
       </c>
       <c r="B2450" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2451">
       <c r="A2451" t="inlineStr">
         <is>
-          <t>MTH900BM</t>
+          <t>MTH900AS</t>
         </is>
       </c>
       <c r="B2451" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2452">
       <c r="A2452" t="inlineStr">
         <is>
-          <t>MTH900BS</t>
+          <t>MTH900BM</t>
         </is>
       </c>
       <c r="B2452" t="n">
@@ -24785,24 +24950,27 @@
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>MXA73N</t>
+          <t>MTH900BS</t>
         </is>
       </c>
       <c r="B2453" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2454">
       <c r="A2454" t="inlineStr">
         <is>
-          <t>MXS55BNBSL</t>
-        </is>
+          <t>MXA73N</t>
+        </is>
+      </c>
+      <c r="B2454" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="2455">
       <c r="A2455" t="inlineStr">
         <is>
-          <t>PAL146</t>
+          <t>MXS55BNBSL</t>
         </is>
       </c>
       <c r="B2455" t="n">
@@ -24812,7 +24980,7 @@
     <row r="2456">
       <c r="A2456" t="inlineStr">
         <is>
-          <t>PBC146MNC</t>
+          <t>PAL146</t>
         </is>
       </c>
       <c r="B2456" t="n">
@@ -24822,7 +24990,7 @@
     <row r="2457">
       <c r="A2457" t="inlineStr">
         <is>
-          <t>PBR146</t>
+          <t>PBC146MNC</t>
         </is>
       </c>
       <c r="B2457" t="n">
@@ -24832,7 +25000,7 @@
     <row r="2458">
       <c r="A2458" t="inlineStr">
         <is>
-          <t>PCP147</t>
+          <t>PBR146</t>
         </is>
       </c>
       <c r="B2458" t="n">
@@ -24842,7 +25010,7 @@
     <row r="2459">
       <c r="A2459" t="inlineStr">
         <is>
-          <t>PMM146STM</t>
+          <t>PCP147</t>
         </is>
       </c>
       <c r="B2459" t="n">
@@ -24852,7 +25020,7 @@
     <row r="2460">
       <c r="A2460" t="inlineStr">
         <is>
-          <t>POWERGLIDE</t>
+          <t>PMM146STM</t>
         </is>
       </c>
       <c r="B2460" t="n">
@@ -24862,7 +25030,7 @@
     <row r="2461">
       <c r="A2461" t="inlineStr">
         <is>
-          <t>PST146</t>
+          <t>POWERGLIDE</t>
         </is>
       </c>
       <c r="B2461" t="n">
@@ -24872,47 +25040,47 @@
     <row r="2462">
       <c r="A2462" t="inlineStr">
         <is>
-          <t>QC8 B4</t>
+          <t>PST146</t>
         </is>
       </c>
       <c r="B2462" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2463">
       <c r="A2463" t="inlineStr">
         <is>
-          <t>QC8B4GY</t>
+          <t>QC8 B4</t>
         </is>
       </c>
       <c r="B2463" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2464">
       <c r="A2464" t="inlineStr">
         <is>
-          <t>QC8B4OR</t>
+          <t>QC8B4GY</t>
         </is>
       </c>
       <c r="B2464" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2465">
       <c r="A2465" t="inlineStr">
         <is>
-          <t>QC8B4PU</t>
+          <t>QC8B4OR</t>
         </is>
       </c>
       <c r="B2465" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2466">
       <c r="A2466" t="inlineStr">
         <is>
-          <t>QC8C</t>
+          <t>QC8B4PU</t>
         </is>
       </c>
       <c r="B2466" t="n">
@@ -24922,7 +25090,7 @@
     <row r="2467">
       <c r="A2467" t="inlineStr">
         <is>
-          <t>QHC7</t>
+          <t>QC8C</t>
         </is>
       </c>
       <c r="B2467" t="n">
@@ -24932,14 +25100,17 @@
     <row r="2468">
       <c r="A2468" t="inlineStr">
         <is>
-          <t>REDOBLANTE</t>
-        </is>
+          <t>QHC7</t>
+        </is>
+      </c>
+      <c r="B2468" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2469">
       <c r="A2469" t="inlineStr">
         <is>
-          <t>RLI52KH4CB</t>
+          <t>REDOBLANTE</t>
         </is>
       </c>
       <c r="B2469" t="n">
@@ -24949,7 +25120,7 @@
     <row r="2470">
       <c r="A2470" t="inlineStr">
         <is>
-          <t>RLI52KH4FF</t>
+          <t>RLI52KH4CB</t>
         </is>
       </c>
       <c r="B2470" t="n">
@@ -24959,7 +25130,7 @@
     <row r="2471">
       <c r="A2471" t="inlineStr">
         <is>
-          <t>RLI52KH4SW</t>
+          <t>RLI52KH4FF</t>
         </is>
       </c>
       <c r="B2471" t="n">
@@ -24969,7 +25140,7 @@
     <row r="2472">
       <c r="A2472" t="inlineStr">
         <is>
-          <t>RM52KH4BK</t>
+          <t>RLI52KH4SW</t>
         </is>
       </c>
       <c r="B2472" t="n">
@@ -24979,7 +25150,7 @@
     <row r="2473">
       <c r="A2473" t="inlineStr">
         <is>
-          <t>RM52KH4CCM</t>
+          <t>RM52KH4BK</t>
         </is>
       </c>
       <c r="B2473" t="n">
@@ -24989,7 +25160,7 @@
     <row r="2474">
       <c r="A2474" t="inlineStr">
         <is>
-          <t>RM52KH4GXS</t>
+          <t>RM52KH4CCM</t>
         </is>
       </c>
       <c r="B2474" t="n">
@@ -24999,7 +25170,7 @@
     <row r="2475">
       <c r="A2475" t="inlineStr">
         <is>
-          <t>RMI52KH4BK</t>
+          <t>RM52KH4GXS</t>
         </is>
       </c>
       <c r="B2475" t="n">
@@ -25009,7 +25180,7 @@
     <row r="2476">
       <c r="A2476" t="inlineStr">
         <is>
-          <t>RMI52KH4GX</t>
+          <t>RMI52KH4BK</t>
         </is>
       </c>
       <c r="B2476" t="n">
@@ -25019,7 +25190,7 @@
     <row r="2477">
       <c r="A2477" t="inlineStr">
         <is>
-          <t>RMI52KH4HL</t>
+          <t>RMI52KH4GX</t>
         </is>
       </c>
       <c r="B2477" t="n">
@@ -25029,7 +25200,7 @@
     <row r="2478">
       <c r="A2478" t="inlineStr">
         <is>
-          <t>RMI52KH4RD</t>
+          <t>RMI52KH4HL</t>
         </is>
       </c>
       <c r="B2478" t="n">
@@ -25039,7 +25210,7 @@
     <row r="2479">
       <c r="A2479" t="inlineStr">
         <is>
-          <t>RSS1455</t>
+          <t>RMI52KH4RD</t>
         </is>
       </c>
       <c r="B2479" t="n">
@@ -25049,27 +25220,27 @@
     <row r="2480">
       <c r="A2480" t="inlineStr">
         <is>
-          <t>RWH10</t>
+          <t>RSS1455</t>
         </is>
       </c>
       <c r="B2480" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2481">
       <c r="A2481" t="inlineStr">
         <is>
-          <t>S52KH4BK</t>
+          <t>RWH10</t>
         </is>
       </c>
       <c r="B2481" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2482">
       <c r="A2482" t="inlineStr">
         <is>
-          <t>S52KH4VTR</t>
+          <t>S52KH4BK</t>
         </is>
       </c>
       <c r="B2482" t="n">
@@ -25079,7 +25250,7 @@
     <row r="2483">
       <c r="A2483" t="inlineStr">
         <is>
-          <t>S812SH</t>
+          <t>S52KH4VTR</t>
         </is>
       </c>
       <c r="B2483" t="n">
@@ -25089,7 +25260,7 @@
     <row r="2484">
       <c r="A2484" t="inlineStr">
         <is>
-          <t>SG52KH4CBK</t>
+          <t>S812SH</t>
         </is>
       </c>
       <c r="B2484" t="n">
@@ -25099,7 +25270,7 @@
     <row r="2485">
       <c r="A2485" t="inlineStr">
         <is>
-          <t>SM5W</t>
+          <t>SG52KH4CBK</t>
         </is>
       </c>
       <c r="B2485" t="n">
@@ -25109,14 +25280,17 @@
     <row r="2486">
       <c r="A2486" t="inlineStr">
         <is>
-          <t>SP910CB</t>
-        </is>
+          <t>SM5W</t>
+        </is>
+      </c>
+      <c r="B2486" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2487">
       <c r="A2487" t="inlineStr">
         <is>
-          <t>SPIC50TH</t>
+          <t>SP910CB</t>
         </is>
       </c>
       <c r="B2487" t="n">
@@ -25126,7 +25300,7 @@
     <row r="2488">
       <c r="A2488" t="inlineStr">
         <is>
-          <t>ST52H4BNS</t>
+          <t>SPIC50TH</t>
         </is>
       </c>
       <c r="B2488" t="n">
@@ -25136,7 +25310,7 @@
     <row r="2489">
       <c r="A2489" t="inlineStr">
         <is>
-          <t>ST52H4CBNS</t>
+          <t>ST52H4BNS</t>
         </is>
       </c>
       <c r="B2489" t="n">
@@ -25146,7 +25320,7 @@
     <row r="2490">
       <c r="A2490" t="inlineStr">
         <is>
-          <t>ST52H4CCDS</t>
+          <t>ST52H4CBNS</t>
         </is>
       </c>
       <c r="B2490" t="n">
@@ -25156,7 +25330,7 @@
     <row r="2491">
       <c r="A2491" t="inlineStr">
         <is>
-          <t>ST52H4CCSS</t>
+          <t>ST52H4CCDS</t>
         </is>
       </c>
       <c r="B2491" t="n">
@@ -25166,7 +25340,7 @@
     <row r="2492">
       <c r="A2492" t="inlineStr">
         <is>
-          <t>ST52H4CDS</t>
+          <t>ST52H4CCSS</t>
         </is>
       </c>
       <c r="B2492" t="n">
@@ -25176,7 +25350,7 @@
     <row r="2493">
       <c r="A2493" t="inlineStr">
         <is>
-          <t>ST52H4CLGS</t>
+          <t>ST52H4CDS</t>
         </is>
       </c>
       <c r="B2493" t="n">
@@ -25186,7 +25360,7 @@
     <row r="2494">
       <c r="A2494" t="inlineStr">
         <is>
-          <t>ST52H4CSCP</t>
+          <t>ST52H4CLGS</t>
         </is>
       </c>
       <c r="B2494" t="n">
@@ -25196,7 +25370,7 @@
     <row r="2495">
       <c r="A2495" t="inlineStr">
         <is>
-          <t>ST52H4CSEM</t>
+          <t>ST52H4CSCP</t>
         </is>
       </c>
       <c r="B2495" t="n">
@@ -25206,7 +25380,7 @@
     <row r="2496">
       <c r="A2496" t="inlineStr">
         <is>
-          <t>ST52H4CSS</t>
+          <t>ST52H4CSEM</t>
         </is>
       </c>
       <c r="B2496" t="n">
@@ -25216,7 +25390,7 @@
     <row r="2497">
       <c r="A2497" t="inlineStr">
         <is>
-          <t>ST52H4LGS</t>
+          <t>ST52H4CSS</t>
         </is>
       </c>
       <c r="B2497" t="n">
@@ -25226,17 +25400,17 @@
     <row r="2498">
       <c r="A2498" t="inlineStr">
         <is>
-          <t>ST52H4SCP</t>
+          <t>ST52H4LGS</t>
         </is>
       </c>
       <c r="B2498" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2499">
       <c r="A2499" t="inlineStr">
         <is>
-          <t>ST52H4SEM</t>
+          <t>ST52H4SCP</t>
         </is>
       </c>
       <c r="B2499" t="n">
@@ -25246,7 +25420,7 @@
     <row r="2500">
       <c r="A2500" t="inlineStr">
         <is>
-          <t>ST52H5CBNS</t>
+          <t>ST52H4SEM</t>
         </is>
       </c>
       <c r="B2500" t="n">
@@ -25256,7 +25430,7 @@
     <row r="2501">
       <c r="A2501" t="inlineStr">
         <is>
-          <t>ST52H5CCDS</t>
+          <t>ST52H5CBNS</t>
         </is>
       </c>
       <c r="B2501" t="n">
@@ -25266,7 +25440,7 @@
     <row r="2502">
       <c r="A2502" t="inlineStr">
         <is>
-          <t>ST52H5CCSS</t>
+          <t>ST52H5CCDS</t>
         </is>
       </c>
       <c r="B2502" t="n">
@@ -25276,7 +25450,7 @@
     <row r="2503">
       <c r="A2503" t="inlineStr">
         <is>
-          <t>ST52H5CLGS</t>
+          <t>ST52H5CCSS</t>
         </is>
       </c>
       <c r="B2503" t="n">
@@ -25286,7 +25460,7 @@
     <row r="2504">
       <c r="A2504" t="inlineStr">
         <is>
-          <t>ST52H5CSCP</t>
+          <t>ST52H5CLGS</t>
         </is>
       </c>
       <c r="B2504" t="n">
@@ -25296,7 +25470,7 @@
     <row r="2505">
       <c r="A2505" t="inlineStr">
         <is>
-          <t>ST52H5CSEM</t>
+          <t>ST52H5CSCP</t>
         </is>
       </c>
       <c r="B2505" t="n">
@@ -25306,7 +25480,7 @@
     <row r="2506">
       <c r="A2506" t="inlineStr">
         <is>
-          <t>STDC7</t>
+          <t>ST52H5CSEM</t>
         </is>
       </c>
       <c r="B2506" t="n">
@@ -25316,7 +25490,7 @@
     <row r="2507">
       <c r="A2507" t="inlineStr">
         <is>
-          <t>TAT10</t>
+          <t>STDC7</t>
         </is>
       </c>
       <c r="B2507" t="n">
@@ -25326,47 +25500,47 @@
     <row r="2508">
       <c r="A2508" t="inlineStr">
         <is>
-          <t>TDK03</t>
+          <t>TAT10</t>
         </is>
       </c>
       <c r="B2508" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2509">
       <c r="A2509" t="inlineStr">
         <is>
-          <t>TDK05</t>
+          <t>TDK03</t>
         </is>
       </c>
       <c r="B2509" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2510">
       <c r="A2510" t="inlineStr">
         <is>
-          <t>TDK10</t>
+          <t>TDK05</t>
         </is>
       </c>
       <c r="B2510" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2511">
       <c r="A2511" t="inlineStr">
         <is>
-          <t>TDK10BN</t>
+          <t>TDK10</t>
         </is>
       </c>
       <c r="B2511" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2512">
       <c r="A2512" t="inlineStr">
         <is>
-          <t>TDK10GR</t>
+          <t>TDK10BN</t>
         </is>
       </c>
       <c r="B2512" t="n">
@@ -25376,27 +25550,27 @@
     <row r="2513">
       <c r="A2513" t="inlineStr">
         <is>
-          <t>TIBL1</t>
+          <t>TDK10GR</t>
         </is>
       </c>
       <c r="B2513" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2514">
       <c r="A2514" t="inlineStr">
         <is>
-          <t>TT4S</t>
+          <t>TIBL1</t>
         </is>
       </c>
       <c r="B2514" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2515">
       <c r="A2515" t="inlineStr">
         <is>
-          <t>TTB30F</t>
+          <t>TT4S</t>
         </is>
       </c>
       <c r="B2515" t="n">
@@ -25406,7 +25580,7 @@
     <row r="2516">
       <c r="A2516" t="inlineStr">
         <is>
-          <t>TTL10</t>
+          <t>TTB30F</t>
         </is>
       </c>
       <c r="B2516" t="n">
@@ -25416,7 +25590,7 @@
     <row r="2517">
       <c r="A2517" t="inlineStr">
         <is>
-          <t>TTP4BK</t>
+          <t>TTL10</t>
         </is>
       </c>
       <c r="B2517" t="n">
@@ -25426,17 +25600,17 @@
     <row r="2518">
       <c r="A2518" t="inlineStr">
         <is>
-          <t>TTP4PK</t>
+          <t>TTP4BK</t>
         </is>
       </c>
       <c r="B2518" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2519">
       <c r="A2519" t="inlineStr">
         <is>
-          <t>TTP4YL</t>
+          <t>TTP4PK</t>
         </is>
       </c>
       <c r="B2519" t="n">
@@ -25446,17 +25620,17 @@
     <row r="2520">
       <c r="A2520" t="inlineStr">
         <is>
-          <t>TTSD10</t>
+          <t>TTP4YL</t>
         </is>
       </c>
       <c r="B2520" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2521">
       <c r="A2521" t="inlineStr">
         <is>
-          <t>TW100</t>
+          <t>TTSD10</t>
         </is>
       </c>
       <c r="B2521" t="n">
@@ -25466,7 +25640,7 @@
     <row r="2522">
       <c r="A2522" t="inlineStr">
         <is>
-          <t>TW200</t>
+          <t>TW100</t>
         </is>
       </c>
       <c r="B2522" t="n">
@@ -25476,17 +25650,17 @@
     <row r="2523">
       <c r="A2523" t="inlineStr">
         <is>
-          <t>VD36MWSBCB</t>
+          <t>TW200</t>
         </is>
       </c>
       <c r="B2523" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2524">
       <c r="A2524" t="inlineStr">
         <is>
-          <t>VD36MWSBOS</t>
+          <t>VD36MWSBCB</t>
         </is>
       </c>
       <c r="B2524" t="n">
@@ -25496,37 +25670,37 @@
     <row r="2525">
       <c r="A2525" t="inlineStr">
         <is>
-          <t>VD36MWSMCS</t>
+          <t>VD36MWSBOS</t>
         </is>
       </c>
       <c r="B2525" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2526">
       <c r="A2526" t="inlineStr">
         <is>
-          <t>VD36MWSVBG</t>
+          <t>VD36MWSMCS</t>
         </is>
       </c>
       <c r="B2526" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2527">
       <c r="A2527" t="inlineStr">
         <is>
-          <t>VD36MWSWSP</t>
+          <t>VD36MWSVBG</t>
         </is>
       </c>
       <c r="B2527" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2528">
       <c r="A2528" t="inlineStr">
         <is>
-          <t>VD40VSISP</t>
+          <t>VD36MWSWSP</t>
         </is>
       </c>
       <c r="B2528" t="n">
@@ -25536,7 +25710,7 @@
     <row r="2529">
       <c r="A2529" t="inlineStr">
         <is>
-          <t>VD40VSVBG</t>
+          <t>VD40VSISP</t>
         </is>
       </c>
       <c r="B2529" t="n">
@@ -25546,7 +25720,7 @@
     <row r="2530">
       <c r="A2530" t="inlineStr">
         <is>
-          <t>VD48SDRP</t>
+          <t>VD40VSVBG</t>
         </is>
       </c>
       <c r="B2530" t="n">
@@ -25556,7 +25730,7 @@
     <row r="2531">
       <c r="A2531" t="inlineStr">
         <is>
-          <t>VD52KRSBCB</t>
+          <t>VD48SDRP</t>
         </is>
       </c>
       <c r="B2531" t="n">
@@ -25566,7 +25740,7 @@
     <row r="2532">
       <c r="A2532" t="inlineStr">
         <is>
-          <t>VD52KRSVBG</t>
+          <t>VD52KRSBCB</t>
         </is>
       </c>
       <c r="B2532" t="n">
@@ -25576,7 +25750,7 @@
     <row r="2533">
       <c r="A2533" t="inlineStr">
         <is>
-          <t>VD62RSISP</t>
+          <t>VD52KRSVBG</t>
         </is>
       </c>
       <c r="B2533" t="n">
@@ -25586,7 +25760,7 @@
     <row r="2534">
       <c r="A2534" t="inlineStr">
         <is>
-          <t>VD62RSVBG</t>
+          <t>VD62RSISP</t>
         </is>
       </c>
       <c r="B2534" t="n">
@@ -25596,7 +25770,7 @@
     <row r="2535">
       <c r="A2535" t="inlineStr">
         <is>
-          <t>VK36MWSBCB</t>
+          <t>VD62RSVBG</t>
         </is>
       </c>
       <c r="B2535" t="n">
@@ -25606,7 +25780,7 @@
     <row r="2536">
       <c r="A2536" t="inlineStr">
         <is>
-          <t>VK52KSBK</t>
+          <t>VK36MWSBCB</t>
         </is>
       </c>
       <c r="B2536" t="n">
@@ -25616,7 +25790,7 @@
     <row r="2537">
       <c r="A2537" t="inlineStr">
         <is>
-          <t>VK52KSVBG</t>
+          <t>VK52KSBK</t>
         </is>
       </c>
       <c r="B2537" t="n">
@@ -25626,7 +25800,7 @@
     <row r="2538">
       <c r="A2538" t="inlineStr">
         <is>
-          <t>VK52ZGRSIS</t>
+          <t>VK52KSVBG</t>
         </is>
       </c>
       <c r="B2538" t="n">
@@ -25636,7 +25810,7 @@
     <row r="2539">
       <c r="A2539" t="inlineStr">
         <is>
-          <t>VK62SVBG</t>
+          <t>VK52ZGRSIS</t>
         </is>
       </c>
       <c r="B2539" t="n">
@@ -25646,7 +25820,7 @@
     <row r="2540">
       <c r="A2540" t="inlineStr">
         <is>
-          <t>VK62SWSP</t>
+          <t>VK62SVBG</t>
         </is>
       </c>
       <c r="B2540" t="n">
@@ -25656,21 +25830,27 @@
     <row r="2541">
       <c r="A2541" t="inlineStr">
         <is>
-          <t>VKF14ASKS</t>
-        </is>
+          <t>VK62SWSP</t>
+        </is>
+      </c>
+      <c r="B2541" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2542">
       <c r="A2542" t="inlineStr">
         <is>
-          <t>VKT8ASKS</t>
-        </is>
+          <t>VKF14ASKS</t>
+        </is>
+      </c>
+      <c r="B2542" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2543">
       <c r="A2543" t="inlineStr">
         <is>
-          <t>VL52KSDMF</t>
+          <t>VKT8ASKS</t>
         </is>
       </c>
       <c r="B2543" t="n">
@@ -25680,7 +25860,7 @@
     <row r="2544">
       <c r="A2544" t="inlineStr">
         <is>
-          <t>VL52KSTRB</t>
+          <t>VL52KSDMF</t>
         </is>
       </c>
       <c r="B2544" t="n">
@@ -25690,7 +25870,7 @@
     <row r="2545">
       <c r="A2545" t="inlineStr">
         <is>
-          <t>VL62SABB</t>
+          <t>VL52KSTRB</t>
         </is>
       </c>
       <c r="B2545" t="n">
@@ -25700,7 +25880,7 @@
     <row r="2546">
       <c r="A2546" t="inlineStr">
         <is>
-          <t>VL62SDMF</t>
+          <t>VL62SABB</t>
         </is>
       </c>
       <c r="B2546" t="n">
@@ -25710,42 +25890,57 @@
     <row r="2547">
       <c r="A2547" t="inlineStr">
         <is>
-          <t>VLB22ETRB</t>
-        </is>
+          <t>VL62SDMF</t>
+        </is>
+      </c>
+      <c r="B2547" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2548">
       <c r="A2548" t="inlineStr">
         <is>
-          <t>VLF14ATRB</t>
-        </is>
+          <t>VLB22ETRB</t>
+        </is>
+      </c>
+      <c r="B2548" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2549">
       <c r="A2549" t="inlineStr">
         <is>
-          <t>VLF18DTRB</t>
-        </is>
+          <t>VLF14ATRB</t>
+        </is>
+      </c>
+      <c r="B2549" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2550">
       <c r="A2550" t="inlineStr">
         <is>
-          <t>VLT13ATRB</t>
-        </is>
+          <t>VLF18DTRB</t>
+        </is>
+      </c>
+      <c r="B2550" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2551">
       <c r="A2551" t="inlineStr">
         <is>
-          <t>VLT8ATRB</t>
-        </is>
+          <t>VLT13ATRB</t>
+        </is>
+      </c>
+      <c r="B2551" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2552">
       <c r="A2552" t="inlineStr">
         <is>
-          <t>VP48SABR</t>
+          <t>VLT8ATRB</t>
         </is>
       </c>
       <c r="B2552" t="n">
@@ -25755,17 +25950,17 @@
     <row r="2553">
       <c r="A2553" t="inlineStr">
         <is>
-          <t>VP48SJTB</t>
+          <t>VP48SABR</t>
         </is>
       </c>
       <c r="B2553" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2554">
       <c r="A2554" t="inlineStr">
         <is>
-          <t>VP48SVGD</t>
+          <t>VP48SJTB</t>
         </is>
       </c>
       <c r="B2554" t="n">
@@ -25775,7 +25970,7 @@
     <row r="2555">
       <c r="A2555" t="inlineStr">
         <is>
-          <t>VP52KRSABR</t>
+          <t>VP48SVGD</t>
         </is>
       </c>
       <c r="B2555" t="n">
@@ -25785,7 +25980,7 @@
     <row r="2556">
       <c r="A2556" t="inlineStr">
         <is>
-          <t>VP52KRSDMF</t>
+          <t>VP52KRSABR</t>
         </is>
       </c>
       <c r="B2556" t="n">
@@ -25795,7 +25990,7 @@
     <row r="2557">
       <c r="A2557" t="inlineStr">
         <is>
-          <t>VP52KRSJTB</t>
+          <t>VP52KRSDMF</t>
         </is>
       </c>
       <c r="B2557" t="n">
@@ -25805,7 +26000,7 @@
     <row r="2558">
       <c r="A2558" t="inlineStr">
         <is>
-          <t>VP52KRSTRB</t>
+          <t>VP52KRSJTB</t>
         </is>
       </c>
       <c r="B2558" t="n">
@@ -25815,7 +26010,7 @@
     <row r="2559">
       <c r="A2559" t="inlineStr">
         <is>
-          <t>VP62RSABR</t>
+          <t>VP52KRSTRB</t>
         </is>
       </c>
       <c r="B2559" t="n">
@@ -25825,7 +26020,7 @@
     <row r="2560">
       <c r="A2560" t="inlineStr">
         <is>
-          <t>VP62RSDMF</t>
+          <t>VP62RSABR</t>
         </is>
       </c>
       <c r="B2560" t="n">
@@ -25835,21 +26030,27 @@
     <row r="2561">
       <c r="A2561" t="inlineStr">
         <is>
-          <t>VP62RSJTB</t>
-        </is>
+          <t>VP62RSDMF</t>
+        </is>
+      </c>
+      <c r="B2561" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2562">
       <c r="A2562" t="inlineStr">
         <is>
-          <t>WBR30RSCCO</t>
-        </is>
+          <t>VP62RSJTB</t>
+        </is>
+      </c>
+      <c r="B2562" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2563">
       <c r="A2563" t="inlineStr">
         <is>
-          <t>WBR30RSVMP</t>
+          <t>WBR30RSCCO</t>
         </is>
       </c>
       <c r="B2563" t="n">
@@ -25859,7 +26060,7 @@
     <row r="2564">
       <c r="A2564" t="inlineStr">
         <is>
-          <t>WBR32RSCCO</t>
+          <t>WBR30RSVMP</t>
         </is>
       </c>
       <c r="B2564" t="n">
@@ -25869,7 +26070,7 @@
     <row r="2565">
       <c r="A2565" t="inlineStr">
         <is>
-          <t>WBR32RZSRO</t>
+          <t>WBR32RSCCO</t>
         </is>
       </c>
       <c r="B2565" t="n">
@@ -25879,7 +26080,7 @@
     <row r="2566">
       <c r="A2566" t="inlineStr">
         <is>
-          <t>WBR32RZSTQ</t>
+          <t>WBR32RZSRO</t>
         </is>
       </c>
       <c r="B2566" t="n">
@@ -25889,27 +26090,27 @@
     <row r="2567">
       <c r="A2567" t="inlineStr">
         <is>
-          <t>WBR42SCCO</t>
+          <t>WBR32RZSTQ</t>
         </is>
       </c>
       <c r="B2567" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2568">
       <c r="A2568" t="inlineStr">
         <is>
-          <t>WBR42SROY</t>
+          <t>WBR42SCCO</t>
         </is>
       </c>
       <c r="B2568" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2569">
       <c r="A2569" t="inlineStr">
         <is>
-          <t>WBR42STQP</t>
+          <t>WBR42SROY</t>
         </is>
       </c>
       <c r="B2569" t="n">
@@ -25919,52 +26120,67 @@
     <row r="2570">
       <c r="A2570" t="inlineStr">
         <is>
-          <t>WBR42SVMP</t>
+          <t>WBR42STQP</t>
         </is>
       </c>
       <c r="B2570" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2571">
       <c r="A2571" t="inlineStr">
         <is>
-          <t>WBRB18RMCO</t>
-        </is>
+          <t>WBR42SVMP</t>
+        </is>
+      </c>
+      <c r="B2571" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="2572">
       <c r="A2572" t="inlineStr">
         <is>
-          <t>WBRB22DMCO</t>
-        </is>
+          <t>WBRB18RMCO</t>
+        </is>
+      </c>
+      <c r="B2572" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2573">
       <c r="A2573" t="inlineStr">
         <is>
-          <t>WBRB24DMCO</t>
-        </is>
+          <t>WBRB22DMCO</t>
+        </is>
+      </c>
+      <c r="B2573" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2574">
       <c r="A2574" t="inlineStr">
         <is>
-          <t>WBRF16DCCO</t>
-        </is>
+          <t>WBRB24DMCO</t>
+        </is>
+      </c>
+      <c r="B2574" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2575">
       <c r="A2575" t="inlineStr">
         <is>
-          <t>WBRF18DCCO</t>
-        </is>
+          <t>WBRF16DCCO</t>
+        </is>
+      </c>
+      <c r="B2575" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2576">
       <c r="A2576" t="inlineStr">
         <is>
-          <t>WBRF18DROY</t>
+          <t>WBRF18DCCO</t>
         </is>
       </c>
       <c r="B2576" t="n">
@@ -25974,21 +26190,27 @@
     <row r="2577">
       <c r="A2577" t="inlineStr">
         <is>
-          <t>WBRS136CCO</t>
-        </is>
+          <t>WBRF18DROY</t>
+        </is>
+      </c>
+      <c r="B2577" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2578">
       <c r="A2578" t="inlineStr">
         <is>
-          <t>WBRS55CCO</t>
-        </is>
+          <t>WBRS136CCO</t>
+        </is>
+      </c>
+      <c r="B2578" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2579">
       <c r="A2579" t="inlineStr">
         <is>
-          <t>WBRS65ROY</t>
+          <t>WBRS55CCO</t>
         </is>
       </c>
       <c r="B2579" t="n">
@@ -25998,28 +26220,37 @@
     <row r="2580">
       <c r="A2580" t="inlineStr">
         <is>
-          <t>WBRT13ACCO</t>
-        </is>
+          <t>WBRS65ROY</t>
+        </is>
+      </c>
+      <c r="B2580" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2581">
       <c r="A2581" t="inlineStr">
         <is>
-          <t>WBRT14ACCO</t>
-        </is>
+          <t>WBRT13ACCO</t>
+        </is>
+      </c>
+      <c r="B2581" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2582">
       <c r="A2582" t="inlineStr">
         <is>
-          <t>WBRT8ACCO</t>
-        </is>
+          <t>WBRT14ACCO</t>
+        </is>
+      </c>
+      <c r="B2582" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="2583">
       <c r="A2583" t="inlineStr">
         <is>
-          <t>WBS52MBR</t>
+          <t>WBRT8ACCO</t>
         </is>
       </c>
       <c r="B2583" t="n">
@@ -26029,7 +26260,7 @@
     <row r="2584">
       <c r="A2584" t="inlineStr">
         <is>
-          <t>WBS52RZVBF</t>
+          <t>WBS52MBR</t>
         </is>
       </c>
       <c r="B2584" t="n">
@@ -26039,7 +26270,7 @@
     <row r="2585">
       <c r="A2585" t="inlineStr">
         <is>
-          <t>WBS52SAF</t>
+          <t>WBS52RZVBF</t>
         </is>
       </c>
       <c r="B2585" t="n">
@@ -26049,27 +26280,27 @@
     <row r="2586">
       <c r="A2586" t="inlineStr">
         <is>
-          <t>WBS52SPF</t>
+          <t>WBS52SAF</t>
         </is>
       </c>
       <c r="B2586" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2587">
       <c r="A2587" t="inlineStr">
         <is>
-          <t>WBSS65BVBF</t>
+          <t>WBS52SPF</t>
         </is>
       </c>
       <c r="B2587" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2588">
       <c r="A2588" t="inlineStr">
         <is>
-          <t>WBSS65MBR</t>
+          <t>WBSS65BVBF</t>
         </is>
       </c>
       <c r="B2588" t="n">
@@ -26079,7 +26310,7 @@
     <row r="2589">
       <c r="A2589" t="inlineStr">
         <is>
-          <t>WBSS65SAF</t>
+          <t>WBSS65MBR</t>
         </is>
       </c>
       <c r="B2589" t="n">
@@ -26089,24 +26320,27 @@
     <row r="2590">
       <c r="A2590" t="inlineStr">
         <is>
-          <t>WBSS65SPF</t>
+          <t>WBSS65SAF</t>
         </is>
       </c>
       <c r="B2590" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2591">
       <c r="A2591" t="inlineStr">
         <is>
-          <t>WBST10RPBK</t>
-        </is>
+          <t>WBSS65SPF</t>
+        </is>
+      </c>
+      <c r="B2591" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="2592">
       <c r="A2592" t="inlineStr">
         <is>
-          <t>WP1465BKBO</t>
+          <t>WBST10RPBK</t>
         </is>
       </c>
       <c r="B2592" t="n">
@@ -26116,17 +26350,17 @@
     <row r="2593">
       <c r="A2593" t="inlineStr">
         <is>
-          <t>JUS10BK</t>
+          <t>WP1465BKBO</t>
         </is>
       </c>
       <c r="B2593" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2594">
       <c r="A2594" t="inlineStr">
         <is>
-          <t>JUS10BL</t>
+          <t>JUS10BK</t>
         </is>
       </c>
       <c r="B2594" t="n">
@@ -26136,7 +26370,7 @@
     <row r="2595">
       <c r="A2595" t="inlineStr">
         <is>
-          <t>JUS10LB</t>
+          <t>JUS10BL</t>
         </is>
       </c>
       <c r="B2595" t="n">
@@ -26146,7 +26380,7 @@
     <row r="2596">
       <c r="A2596" t="inlineStr">
         <is>
-          <t>JUS10RD</t>
+          <t>JUS10LB</t>
         </is>
       </c>
       <c r="B2596" t="n">
@@ -26156,47 +26390,47 @@
     <row r="2597">
       <c r="A2597" t="inlineStr">
         <is>
-          <t>JUS10VIO</t>
+          <t>JUS10RD</t>
         </is>
       </c>
       <c r="B2597" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2598">
       <c r="A2598" t="inlineStr">
         <is>
-          <t>ACOUSTICK</t>
+          <t>JUS10VIO</t>
         </is>
       </c>
       <c r="B2598" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2599">
       <c r="A2599" t="inlineStr">
         <is>
-          <t>P10PR</t>
+          <t>ACOUSTICK</t>
         </is>
       </c>
       <c r="B2599" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2600">
       <c r="A2600" t="inlineStr">
         <is>
-          <t>V BUZZ</t>
+          <t>P10PR</t>
         </is>
       </c>
       <c r="B2600" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2601">
       <c r="A2601" t="inlineStr">
         <is>
-          <t>V BUZZ XD</t>
+          <t>V BUZZ</t>
         </is>
       </c>
       <c r="B2601" t="n">
@@ -26206,17 +26440,17 @@
     <row r="2602">
       <c r="A2602" t="inlineStr">
         <is>
-          <t>VASS</t>
+          <t>V BUZZ XD</t>
         </is>
       </c>
       <c r="B2602" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2603">
       <c r="A2603" t="inlineStr">
         <is>
-          <t>VATER 5AN</t>
+          <t>VASS</t>
         </is>
       </c>
       <c r="B2603" t="n">
@@ -26226,7 +26460,7 @@
     <row r="2604">
       <c r="A2604" t="inlineStr">
         <is>
-          <t>VATER 5AW</t>
+          <t>VATER 5AN</t>
         </is>
       </c>
       <c r="B2604" t="n">
@@ -26236,7 +26470,7 @@
     <row r="2605">
       <c r="A2605" t="inlineStr">
         <is>
-          <t>VATER 5BN</t>
+          <t>VATER 5AW</t>
         </is>
       </c>
       <c r="B2605" t="n">
@@ -26246,7 +26480,7 @@
     <row r="2606">
       <c r="A2606" t="inlineStr">
         <is>
-          <t>VATER 5BW</t>
+          <t>VATER 5BN</t>
         </is>
       </c>
       <c r="B2606" t="n">
@@ -26256,7 +26490,7 @@
     <row r="2607">
       <c r="A2607" t="inlineStr">
         <is>
-          <t>VATER 7AN</t>
+          <t>VATER 5BW</t>
         </is>
       </c>
       <c r="B2607" t="n">
@@ -26266,7 +26500,7 @@
     <row r="2608">
       <c r="A2608" t="inlineStr">
         <is>
-          <t>VATER 7AW</t>
+          <t>VATER 7AN</t>
         </is>
       </c>
       <c r="B2608" t="n">
@@ -26276,17 +26510,17 @@
     <row r="2609">
       <c r="A2609" t="inlineStr">
         <is>
-          <t>VCB5A</t>
+          <t>VATER 7AW</t>
         </is>
       </c>
       <c r="B2609" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2610">
       <c r="A2610" t="inlineStr">
         <is>
-          <t>VCB5B</t>
+          <t>VCB5A</t>
         </is>
       </c>
       <c r="B2610" t="n">
@@ -26296,7 +26530,7 @@
     <row r="2611">
       <c r="A2611" t="inlineStr">
         <is>
-          <t>VCBK5A</t>
+          <t>VCB5B</t>
         </is>
       </c>
       <c r="B2611" t="n">
@@ -26306,7 +26540,7 @@
     <row r="2612">
       <c r="A2612" t="inlineStr">
         <is>
-          <t>VCG5A</t>
+          <t>VCBK5A</t>
         </is>
       </c>
       <c r="B2612" t="n">
@@ -26316,7 +26550,7 @@
     <row r="2613">
       <c r="A2613" t="inlineStr">
         <is>
-          <t>VCG5AN</t>
+          <t>VCG5A</t>
         </is>
       </c>
       <c r="B2613" t="n">
@@ -26326,7 +26560,7 @@
     <row r="2614">
       <c r="A2614" t="inlineStr">
         <is>
-          <t>VCG5B</t>
+          <t>VCG5AN</t>
         </is>
       </c>
       <c r="B2614" t="n">
@@ -26336,7 +26570,7 @@
     <row r="2615">
       <c r="A2615" t="inlineStr">
         <is>
-          <t>VCP5B</t>
+          <t>VCG5B</t>
         </is>
       </c>
       <c r="B2615" t="n">
@@ -26346,7 +26580,7 @@
     <row r="2616">
       <c r="A2616" t="inlineStr">
         <is>
-          <t>VCR5A</t>
+          <t>VCP5B</t>
         </is>
       </c>
       <c r="B2616" t="n">
@@ -26356,7 +26590,7 @@
     <row r="2617">
       <c r="A2617" t="inlineStr">
         <is>
-          <t>VCS5A</t>
+          <t>VCR5A</t>
         </is>
       </c>
       <c r="B2617" t="n">
@@ -26366,7 +26600,7 @@
     <row r="2618">
       <c r="A2618" t="inlineStr">
         <is>
-          <t>VCS5AN</t>
+          <t>VCS5A</t>
         </is>
       </c>
       <c r="B2618" t="n">
@@ -26376,17 +26610,17 @@
     <row r="2619">
       <c r="A2619" t="inlineStr">
         <is>
-          <t>VEP5AN</t>
+          <t>VCS5AN</t>
         </is>
       </c>
       <c r="B2619" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2620">
       <c r="A2620" t="inlineStr">
         <is>
-          <t>VEP5AW</t>
+          <t>VEP5AN</t>
         </is>
       </c>
       <c r="B2620" t="n">
@@ -26396,17 +26630,17 @@
     <row r="2621">
       <c r="A2621" t="inlineStr">
         <is>
-          <t>VGTR</t>
+          <t>VEP5AW</t>
         </is>
       </c>
       <c r="B2621" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2622">
       <c r="A2622" t="inlineStr">
         <is>
-          <t>VGTW</t>
+          <t>VGTR</t>
         </is>
       </c>
       <c r="B2622" t="n">
@@ -26416,7 +26650,7 @@
     <row r="2623">
       <c r="A2623" t="inlineStr">
         <is>
-          <t>VH2BW</t>
+          <t>VGTW</t>
         </is>
       </c>
       <c r="B2623" t="n">
@@ -26426,7 +26660,7 @@
     <row r="2624">
       <c r="A2624" t="inlineStr">
         <is>
-          <t>VH5AAW</t>
+          <t>VH2BW</t>
         </is>
       </c>
       <c r="B2624" t="n">
@@ -26436,17 +26670,17 @@
     <row r="2625">
       <c r="A2625" t="inlineStr">
         <is>
-          <t>VH5AN</t>
+          <t>VH5AAW</t>
         </is>
       </c>
       <c r="B2625" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2626">
       <c r="A2626" t="inlineStr">
         <is>
-          <t>VH5AW</t>
+          <t>VH5AN</t>
         </is>
       </c>
       <c r="B2626" t="n">
@@ -26456,7 +26690,7 @@
     <row r="2627">
       <c r="A2627" t="inlineStr">
         <is>
-          <t>VH5BN</t>
+          <t>VH5AW</t>
         </is>
       </c>
       <c r="B2627" t="n">
@@ -26466,7 +26700,7 @@
     <row r="2628">
       <c r="A2628" t="inlineStr">
         <is>
-          <t>VH5BW</t>
+          <t>VH5BN</t>
         </is>
       </c>
       <c r="B2628" t="n">
@@ -26476,7 +26710,7 @@
     <row r="2629">
       <c r="A2629" t="inlineStr">
         <is>
-          <t>VH7AN</t>
+          <t>VH5BW</t>
         </is>
       </c>
       <c r="B2629" t="n">
@@ -26486,7 +26720,7 @@
     <row r="2630">
       <c r="A2630" t="inlineStr">
         <is>
-          <t>VH7AW</t>
+          <t>VH7AN</t>
         </is>
       </c>
       <c r="B2630" t="n">
@@ -26496,17 +26730,17 @@
     <row r="2631">
       <c r="A2631" t="inlineStr">
         <is>
-          <t>VHBB550</t>
+          <t>VH7AW</t>
         </is>
       </c>
       <c r="B2631" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2632">
       <c r="A2632" t="inlineStr">
         <is>
-          <t>VHCHADW</t>
+          <t>VHBB550</t>
         </is>
       </c>
       <c r="B2632" t="n">
@@ -26516,7 +26750,7 @@
     <row r="2633">
       <c r="A2633" t="inlineStr">
         <is>
-          <t>VHFN</t>
+          <t>VHCHADW</t>
         </is>
       </c>
       <c r="B2633" t="n">
@@ -26526,27 +26760,27 @@
     <row r="2634">
       <c r="A2634" t="inlineStr">
         <is>
-          <t>VHG5AN</t>
+          <t>VHFN</t>
         </is>
       </c>
       <c r="B2634" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2635">
       <c r="A2635" t="inlineStr">
         <is>
-          <t>VHG5AW</t>
+          <t>VHG5AN</t>
         </is>
       </c>
       <c r="B2635" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2636">
       <c r="A2636" t="inlineStr">
         <is>
-          <t>VHK5AW</t>
+          <t>VHG5AW</t>
         </is>
       </c>
       <c r="B2636" t="n">
@@ -26556,7 +26790,7 @@
     <row r="2637">
       <c r="A2637" t="inlineStr">
         <is>
-          <t>VHK5BW</t>
+          <t>VHK5AW</t>
         </is>
       </c>
       <c r="B2637" t="n">
@@ -26566,7 +26800,7 @@
     <row r="2638">
       <c r="A2638" t="inlineStr">
         <is>
-          <t>VHN5W</t>
+          <t>VHK5BW</t>
         </is>
       </c>
       <c r="B2638" t="n">
@@ -26576,7 +26810,7 @@
     <row r="2639">
       <c r="A2639" t="inlineStr">
         <is>
-          <t>VHNSN</t>
+          <t>VHN5W</t>
         </is>
       </c>
       <c r="B2639" t="n">
@@ -26586,7 +26820,7 @@
     <row r="2640">
       <c r="A2640" t="inlineStr">
         <is>
-          <t>VHP5AN</t>
+          <t>VHNSN</t>
         </is>
       </c>
       <c r="B2640" t="n">
@@ -26596,7 +26830,7 @@
     <row r="2641">
       <c r="A2641" t="inlineStr">
         <is>
-          <t>VHP5AW</t>
+          <t>VHP5AN</t>
         </is>
       </c>
       <c r="B2641" t="n">
@@ -26606,7 +26840,7 @@
     <row r="2642">
       <c r="A2642" t="inlineStr">
         <is>
-          <t>VHP5BN</t>
+          <t>VHP5AW</t>
         </is>
       </c>
       <c r="B2642" t="n">
@@ -26616,7 +26850,7 @@
     <row r="2643">
       <c r="A2643" t="inlineStr">
         <is>
-          <t>VHP5BW</t>
+          <t>VHP5BN</t>
         </is>
       </c>
       <c r="B2643" t="n">
@@ -26626,7 +26860,7 @@
     <row r="2644">
       <c r="A2644" t="inlineStr">
         <is>
-          <t>VHPRN</t>
+          <t>VHP5BW</t>
         </is>
       </c>
       <c r="B2644" t="n">
@@ -26636,7 +26870,7 @@
     <row r="2645">
       <c r="A2645" t="inlineStr">
         <is>
-          <t>VHSEW</t>
+          <t>VHPRN</t>
         </is>
       </c>
       <c r="B2645" t="n">
@@ -26646,7 +26880,7 @@
     <row r="2646">
       <c r="A2646" t="inlineStr">
         <is>
-          <t>VHSJW</t>
+          <t>VHSEW</t>
         </is>
       </c>
       <c r="B2646" t="n">
@@ -26656,7 +26890,7 @@
     <row r="2647">
       <c r="A2647" t="inlineStr">
         <is>
-          <t>VHT 1/2</t>
+          <t>VHSJW</t>
         </is>
       </c>
       <c r="B2647" t="n">
@@ -26666,7 +26900,7 @@
     <row r="2648">
       <c r="A2648" t="inlineStr">
         <is>
-          <t>VHT 7/16</t>
+          <t>VHT 1/2</t>
         </is>
       </c>
       <c r="B2648" t="n">
@@ -26676,7 +26910,7 @@
     <row r="2649">
       <c r="A2649" t="inlineStr">
         <is>
-          <t>VMAS</t>
+          <t>VHT 7/16</t>
         </is>
       </c>
       <c r="B2649" t="n">
@@ -26686,7 +26920,7 @@
     <row r="2650">
       <c r="A2650" t="inlineStr">
         <is>
-          <t>VMBN</t>
+          <t>VMAS</t>
         </is>
       </c>
       <c r="B2650" t="n">
@@ -26696,7 +26930,7 @@
     <row r="2651">
       <c r="A2651" t="inlineStr">
         <is>
-          <t>VMBW</t>
+          <t>VMBN</t>
         </is>
       </c>
       <c r="B2651" t="n">
@@ -26706,7 +26940,7 @@
     <row r="2652">
       <c r="A2652" t="inlineStr">
         <is>
-          <t>VMPW</t>
+          <t>VMBW</t>
         </is>
       </c>
       <c r="B2652" t="n">
@@ -26716,7 +26950,7 @@
     <row r="2653">
       <c r="A2653" t="inlineStr">
         <is>
-          <t>VPYB</t>
+          <t>VMPW</t>
         </is>
       </c>
       <c r="B2653" t="n">
@@ -26726,7 +26960,7 @@
     <row r="2654">
       <c r="A2654" t="inlineStr">
         <is>
-          <t>VSAS</t>
+          <t>VPYB</t>
         </is>
       </c>
       <c r="B2654" t="n">
@@ -26736,7 +26970,7 @@
     <row r="2655">
       <c r="A2655" t="inlineStr">
         <is>
-          <t>VSMBB550</t>
+          <t>VSAS</t>
         </is>
       </c>
       <c r="B2655" t="n">
@@ -26746,7 +26980,7 @@
     <row r="2656">
       <c r="A2656" t="inlineStr">
         <is>
-          <t>VSMBB950</t>
+          <t>VSMBB550</t>
         </is>
       </c>
       <c r="B2656" t="n">
@@ -26756,27 +26990,27 @@
     <row r="2657">
       <c r="A2657" t="inlineStr">
         <is>
-          <t>VSNB</t>
+          <t>VSMBB950</t>
         </is>
       </c>
       <c r="B2657" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2658">
       <c r="A2658" t="inlineStr">
         <is>
-          <t>VSPS</t>
+          <t>VSNB</t>
         </is>
       </c>
       <c r="B2658" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2659">
       <c r="A2659" t="inlineStr">
         <is>
-          <t>VSPST</t>
+          <t>VSPS</t>
         </is>
       </c>
       <c r="B2659" t="n">
@@ -26786,7 +27020,7 @@
     <row r="2660">
       <c r="A2660" t="inlineStr">
         <is>
-          <t>VSPSTZ</t>
+          <t>VSPST</t>
         </is>
       </c>
       <c r="B2660" t="n">
@@ -26796,7 +27030,7 @@
     <row r="2661">
       <c r="A2661" t="inlineStr">
         <is>
-          <t>VSTBK</t>
+          <t>VSPSTZ</t>
         </is>
       </c>
       <c r="B2661" t="n">
@@ -26806,17 +27040,17 @@
     <row r="2662">
       <c r="A2662" t="inlineStr">
         <is>
-          <t>VSTR</t>
+          <t>VSTBK</t>
         </is>
       </c>
       <c r="B2662" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2663">
       <c r="A2663" t="inlineStr">
         <is>
-          <t>VWTR</t>
+          <t>VSTR</t>
         </is>
       </c>
       <c r="B2663" t="n">
@@ -26826,10 +27060,20 @@
     <row r="2664">
       <c r="A2664" t="inlineStr">
         <is>
+          <t>VWTR</t>
+        </is>
+      </c>
+      <c r="B2664" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
           <t>WIRETAP</t>
         </is>
       </c>
-      <c r="B2664" t="n">
+      <c r="B2665" t="n">
         <v>0</v>
       </c>
     </row>

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -23124,7 +23124,7 @@
         </is>
       </c>
       <c r="B2270" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2271">
@@ -23134,7 +23134,7 @@
         </is>
       </c>
       <c r="B2271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2272">
@@ -23164,7 +23164,7 @@
         </is>
       </c>
       <c r="B2274" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2275">
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="B2275" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2276">
@@ -23184,7 +23184,7 @@
         </is>
       </c>
       <c r="B2276" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2277">
@@ -23194,7 +23194,7 @@
         </is>
       </c>
       <c r="B2277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2278">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="B2278" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2279">
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="B2279" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2280">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -10624,7 +10624,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1021">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1022">
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1023">
@@ -23514,7 +23514,7 @@
         </is>
       </c>
       <c r="B2309" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2310">
@@ -23684,7 +23684,7 @@
         </is>
       </c>
       <c r="B2326" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2327">

--- a/public_listas/ListaImsa_ULTIMA.xlsx
+++ b/public_listas/ListaImsa_ULTIMA.xlsx
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="576">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="577">
